--- a/बजेट माग estimate/नगर बजेट estimate/लाँकुरी बोट देवी सुमारा सडक/valuation लाँकुरी - Copy.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/लाँकुरी बोट देवी सुमारा सडक/valuation लाँकुरी - Copy.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB7EF21-4825-45C2-BCE9-66FDDC2FEEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF94FDC-DD2C-4D1E-8B9A-F0C67E9AF502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="WCR" sheetId="16" r:id="rId2"/>
     <sheet name="V" sheetId="14" r:id="rId3"/>
-    <sheet name="chainage measurement" sheetId="15" r:id="rId4"/>
+    <sheet name="chainage measurement" sheetId="15" state="hidden" r:id="rId4"/>
+    <sheet name="M" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="description_103">#REF!</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
+    <definedName name="description_124" localSheetId="4">#REF!</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
@@ -26,30 +28,36 @@
     <definedName name="description_276">#REF!</definedName>
     <definedName name="description_3">#REF!</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
+    <definedName name="description_310" localSheetId="4">#REF!</definedName>
     <definedName name="description_310" localSheetId="2">#REF!</definedName>
     <definedName name="description_310" localSheetId="1">#REF!</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
+    <definedName name="description_312" localSheetId="4">#REF!</definedName>
     <definedName name="description_312" localSheetId="2">#REF!</definedName>
     <definedName name="description_312" localSheetId="1">#REF!</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_4">#REF!</definedName>
     <definedName name="description_5">#REF!</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
+    <definedName name="description_6" localSheetId="4">#REF!</definedName>
     <definedName name="description_6" localSheetId="2">#REF!</definedName>
     <definedName name="description_6" localSheetId="1">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">#REF!</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
+    <definedName name="description_781" localSheetId="4">#REF!</definedName>
     <definedName name="description_781" localSheetId="2">#REF!</definedName>
     <definedName name="description_781" localSheetId="1">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">#REF!</definedName>
     <definedName name="description_784">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">M!$A$1:$K$109</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$109</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">M!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
   </definedNames>
@@ -103,8 +111,41 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{87BB8A1F-7190-4979-AD65-AE94DE208860}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+soling stone end</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -335,10 +376,19 @@
     </r>
   </si>
   <si>
-    <t>Date:2083/02/18</t>
+    <t xml:space="preserve">Date:2083/03/18       </t>
   </si>
   <si>
-    <t xml:space="preserve">Date:2083/02/18       </t>
+    <t>Date:2083/03/18</t>
+  </si>
+  <si>
+    <t>Detail Quantity Measurement Sheet</t>
+  </si>
+  <si>
+    <t>Detail Valuated Sheet</t>
+  </si>
+  <si>
+    <t>Total Valuated</t>
   </si>
 </sst>
 </file>
@@ -593,7 +643,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -748,6 +798,30 @@
     <xf numFmtId="1" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,23 +841,26 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -803,27 +880,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1150,113 +1212,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1934,11 +1996,11 @@
       <c r="B41" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="66">
+      <c r="C41" s="74">
         <f>J39</f>
         <v>565661.09314466768</v>
       </c>
-      <c r="D41" s="67"/>
+      <c r="D41" s="75"/>
       <c r="E41" s="33">
         <v>100</v>
       </c>
@@ -1953,21 +2015,21 @@
       <c r="B42" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="70">
+      <c r="C42" s="78">
         <v>500000</v>
       </c>
-      <c r="D42" s="71"/>
+      <c r="D42" s="79"/>
       <c r="E42" s="33"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="70">
+      <c r="C43" s="78">
         <f>C42-C45-C46</f>
         <v>475000</v>
       </c>
-      <c r="D43" s="71"/>
+      <c r="D43" s="79"/>
       <c r="E43" s="33">
         <f>C43/C41*100</f>
         <v>83.972542173502262</v>
@@ -1977,11 +2039,11 @@
       <c r="B44" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="72">
+      <c r="C44" s="80">
         <f>C41-C43</f>
         <v>90661.093144667684</v>
       </c>
-      <c r="D44" s="72"/>
+      <c r="D44" s="80"/>
       <c r="E44" s="33">
         <f>100-E43</f>
         <v>16.027457826497738</v>
@@ -1991,11 +2053,11 @@
       <c r="B45" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="66">
+      <c r="C45" s="74">
         <f>C42*0.03</f>
         <v>15000</v>
       </c>
-      <c r="D45" s="67"/>
+      <c r="D45" s="75"/>
       <c r="E45" s="33">
         <v>3</v>
       </c>
@@ -2004,17 +2066,24 @@
       <c r="B46" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="66">
+      <c r="C46" s="74">
         <f>C42*0.02</f>
         <v>10000</v>
       </c>
-      <c r="D46" s="67"/>
+      <c r="D46" s="75"/>
       <c r="E46" s="33">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="A7:F7"/>
@@ -2023,13 +2092,6 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2062,90 +2124,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
     </row>
     <row r="3" spans="1:13" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
     </row>
     <row r="4" spans="1:13" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="49"/>
-      <c r="C6" s="79">
+      <c r="C6" s="88">
         <f>F34</f>
         <v>565661.09314466768</v>
       </c>
-      <c r="D6" s="80"/>
+      <c r="D6" s="89"/>
       <c r="E6" s="50"/>
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
@@ -2153,11 +2215,11 @@
         <v>58</v>
       </c>
       <c r="I6" s="49"/>
-      <c r="J6" s="79">
+      <c r="J6" s="88">
         <f>I34</f>
-        <v>568312.91840178403</v>
-      </c>
-      <c r="K6" s="80"/>
+        <v>565780.32579845074</v>
+      </c>
+      <c r="K6" s="89"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
@@ -2166,75 +2228,75 @@
       <c r="B7" s="51"/>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="I7" s="86" t="s">
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="I7" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="I8" s="87" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="I8" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="I9" s="87" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="I9" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="C11" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="91" t="s">
+      <c r="D11" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91" t="s">
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="90" t="s">
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="89" t="s">
+      <c r="K11" s="81" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
       <c r="D12" s="52" t="s">
         <v>66</v>
       </c>
@@ -2253,8 +2315,8 @@
       <c r="I12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="90"/>
-      <c r="K12" s="89"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="81"/>
     </row>
     <row r="13" spans="1:13" s="48" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="53">
@@ -2282,11 +2344,11 @@
         <v>1611.6427918317588</v>
       </c>
       <c r="G13" s="54">
-        <f>V!G26</f>
+        <f>V!G24</f>
         <v>22.511609090584113</v>
       </c>
       <c r="H13" s="54">
-        <f>V!I26</f>
+        <f>V!I24</f>
         <v>62.95</v>
       </c>
       <c r="I13" s="54">
@@ -2319,7 +2381,7 @@
       <c r="G14" s="54"/>
       <c r="H14" s="54"/>
       <c r="I14" s="54">
-        <f>V!J27</f>
+        <f>V!J25</f>
         <v>151.3005246978158</v>
       </c>
       <c r="J14" s="55">
@@ -2371,11 +2433,11 @@
         <v>114146.80889972571</v>
       </c>
       <c r="G16" s="54">
-        <f>V!G46</f>
+        <f>V!G40</f>
         <v>19.640222480358585</v>
       </c>
       <c r="H16" s="54">
-        <f>V!I46</f>
+        <f>V!I40</f>
         <v>4458.5200000000004</v>
       </c>
       <c r="I16" s="54">
@@ -2408,7 +2470,7 @@
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
       <c r="I17" s="54">
-        <f>V!J47</f>
+        <f>V!J41</f>
         <v>7566.544976248997</v>
       </c>
       <c r="J17" s="55">
@@ -2460,20 +2522,20 @@
         <v>307236.20847302652</v>
       </c>
       <c r="G19" s="54">
-        <f>V!G66</f>
-        <v>27.673017548078754</v>
+        <f>V!G58</f>
+        <v>27.554400359648305</v>
       </c>
       <c r="H19" s="54">
-        <f>V!I66</f>
+        <f>V!I58</f>
         <v>12000.5</v>
       </c>
       <c r="I19" s="54">
         <f>G19*H19</f>
-        <v>332090.04708571907</v>
+        <v>330666.58151595946</v>
       </c>
       <c r="J19" s="55">
         <f>I19-F19</f>
-        <v>24853.838612692547</v>
+        <v>23430.373042932944</v>
       </c>
       <c r="K19" s="56"/>
       <c r="M19" s="48">
@@ -2497,12 +2559,12 @@
       <c r="G20" s="54"/>
       <c r="H20" s="54"/>
       <c r="I20" s="54">
-        <f>V!J67</f>
-        <v>16282.612212494889</v>
+        <f>V!J59</f>
+        <v>16212.818678862574</v>
       </c>
       <c r="J20" s="55">
         <f>I20-F20</f>
-        <v>1218.6014596756249</v>
+        <v>1148.8079260433096</v>
       </c>
       <c r="K20" s="56"/>
       <c r="M20" s="48">
@@ -2526,12 +2588,12 @@
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
       <c r="I21" s="54">
-        <f>V!J68</f>
-        <v>5140.2408711415901</v>
+        <f>V!J60</f>
+        <v>5118.2078232843842</v>
       </c>
       <c r="J21" s="55">
         <f t="shared" ref="J21:J24" si="3">I21-F21</f>
-        <v>384.69902414372427</v>
+        <v>362.66597628651834</v>
       </c>
       <c r="K21" s="56"/>
     </row>
@@ -2551,12 +2613,12 @@
       <c r="G22" s="54"/>
       <c r="H22" s="54"/>
       <c r="I22" s="54">
-        <f>V!J69</f>
-        <v>10623.164467025954</v>
+        <f>V!J61</f>
+        <v>10577.629501454396</v>
       </c>
       <c r="J22" s="55">
         <f t="shared" si="3"/>
-        <v>795.04464989702865</v>
+        <v>749.50968432547052</v>
       </c>
       <c r="K22" s="56"/>
     </row>
@@ -2576,12 +2638,12 @@
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
       <c r="I23" s="54">
-        <f>V!J70</f>
-        <v>185.8704345312623</v>
+        <f>V!J62</f>
+        <v>185.07372241563777</v>
       </c>
       <c r="J23" s="55">
         <f t="shared" si="3"/>
-        <v>13.910666167958425</v>
+        <v>13.113954052333895</v>
       </c>
       <c r="K23" s="56"/>
     </row>
@@ -2601,12 +2663,12 @@
       <c r="G24" s="54"/>
       <c r="H24" s="54"/>
       <c r="I24" s="54">
-        <f>V!J71</f>
-        <v>1660.4585373338598</v>
+        <f>V!J63</f>
+        <v>1653.3411738999052</v>
       </c>
       <c r="J24" s="55">
         <f t="shared" si="3"/>
-        <v>124.26981438353982</v>
+        <v>117.15245094958527</v>
       </c>
       <c r="K24" s="56"/>
     </row>
@@ -2649,20 +2711,20 @@
         <v>85820.3024691358</v>
       </c>
       <c r="G26" s="54">
-        <f>V!G102</f>
-        <v>0.7214972839506173</v>
+        <f>V!G94</f>
+        <v>0.71455209876543213</v>
       </c>
       <c r="H26" s="54">
-        <f>V!I102</f>
+        <f>V!I94</f>
         <v>124355</v>
       </c>
       <c r="I26" s="54">
         <f>G26*H26</f>
-        <v>89721.794745679013</v>
+        <v>88858.126241975318</v>
       </c>
       <c r="J26" s="55">
         <f>I26-F26</f>
-        <v>3901.4922765432129</v>
+        <v>3037.8237728395179</v>
       </c>
       <c r="K26" s="56"/>
       <c r="M26" s="48">
@@ -2686,12 +2748,12 @@
       <c r="G27" s="54"/>
       <c r="H27" s="54"/>
       <c r="I27" s="54">
-        <f>V!J103</f>
-        <v>10317.411160493828</v>
+        <f>V!J95</f>
+        <v>10218.095012345681</v>
       </c>
       <c r="J27" s="55">
         <f>I27-F27</f>
-        <v>448.64572839506218</v>
+        <v>349.3295802469147</v>
       </c>
       <c r="K27" s="56"/>
       <c r="M27" s="48">
@@ -2715,12 +2777,12 @@
       <c r="G28" s="54"/>
       <c r="H28" s="54"/>
       <c r="I28" s="54">
-        <f>V!J104</f>
-        <v>90.042861037037042</v>
+        <f>V!J96</f>
+        <v>89.176101925925934</v>
       </c>
       <c r="J28" s="55">
         <f>I28-F28</f>
-        <v>3.9154536296296385</v>
+        <v>3.0486945185185306</v>
       </c>
       <c r="K28" s="56"/>
     </row>
@@ -2763,11 +2825,11 @@
         <v>5000</v>
       </c>
       <c r="G30" s="54">
-        <f>V!G106</f>
+        <f>V!G98</f>
         <v>1</v>
       </c>
       <c r="H30" s="54">
-        <f>V!I106</f>
+        <f>V!I98</f>
         <v>5000</v>
       </c>
       <c r="I30" s="54">
@@ -2823,11 +2885,11 @@
         <v>500</v>
       </c>
       <c r="G32" s="54">
-        <f>V!G108</f>
+        <f>V!G100</f>
         <v>1</v>
       </c>
       <c r="H32" s="54">
-        <f>V!I108</f>
+        <f>V!I100</f>
         <v>500</v>
       </c>
       <c r="I32" s="54">
@@ -2869,16 +2931,29 @@
       <c r="H34" s="63"/>
       <c r="I34" s="63">
         <f>SUM(I13:I32)</f>
-        <v>568312.91840178403</v>
+        <v>565780.32579845074</v>
       </c>
       <c r="J34" s="64">
         <f>I34-F34</f>
-        <v>2651.8252571163466</v>
+        <v>119.23265378305223</v>
       </c>
       <c r="K34" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -2886,19 +2961,6 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2914,7 +2976,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF429D35-9056-4106-AB6F-B9EE00C2369D}">
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="3" customWidth="1"/>
@@ -2931,113 +2993,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
+      <c r="A5" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
+      <c r="H7" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -3112,7 +3174,7 @@
         <v>0.12699380270242813</v>
       </c>
       <c r="G10" s="14">
-        <f t="shared" ref="G10:G25" si="0">PRODUCT(C10:F10)</f>
+        <f t="shared" ref="G10:G23" si="0">PRODUCT(C10:F10)</f>
         <v>2.1530113609639026</v>
       </c>
       <c r="H10" s="12"/>
@@ -3469,87 +3531,68 @@
       <c r="J23" s="13"/>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="12">
-        <v>0</v>
-      </c>
-      <c r="D24" s="14">
-        <f>'chainage measurement'!C17</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="14">
-        <f>'chainage measurement'!E17</f>
-        <v>4.4925556232855843</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="G24" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="12"/>
+    <row r="24" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19">
+        <f>SUM(G10:G23)</f>
+        <v>22.511609090584113</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="2">
+        <v>62.95</v>
+      </c>
+      <c r="J24" s="19">
+        <f>G24*I24</f>
+        <v>1417.10579225227</v>
+      </c>
+      <c r="K24" s="18"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="12">
-        <v>0</v>
-      </c>
-      <c r="D25" s="14">
-        <f>'chainage measurement'!C18</f>
-        <v>1</v>
-      </c>
-      <c r="E25" s="14">
-        <f>'chainage measurement'!E18</f>
-        <v>5.6750000000000007</v>
-      </c>
-      <c r="F25" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="G25" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B25" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="13"/>
+      <c r="J25" s="13">
+        <f>0.13*G24*18612/360</f>
+        <v>151.3005246978158</v>
+      </c>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="19">
-        <f>SUM(G10:G25)</f>
-        <v>22.511609090584113</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="2">
-        <v>62.95</v>
-      </c>
-      <c r="J26" s="19">
-        <f>G26*I26</f>
-        <v>1417.10579225227</v>
-      </c>
-      <c r="K26" s="18"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="22" t="s">
-        <v>46</v>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:11" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>2</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -3558,67 +3601,90 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="13">
-        <f>0.13*G26*18612/360</f>
-        <v>151.3005246978158</v>
-      </c>
+      <c r="J27" s="12"/>
       <c r="K27" s="12"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
+      <c r="B28" s="16" t="str">
+        <f>B10</f>
+        <v>-for road</v>
+      </c>
+      <c r="C28" s="12">
+        <f>C10</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <f>D10</f>
+        <v>5</v>
+      </c>
+      <c r="E28" s="14">
+        <f>E10</f>
+        <v>3.3907345321548306</v>
+      </c>
+      <c r="F28" s="14">
+        <f>F10</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G28" s="14">
+        <f t="shared" ref="G28:G39" si="1">PRODUCT(C28:F28)</f>
+        <v>2.1530113609639026</v>
+      </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
       <c r="K28" s="12"/>
     </row>
-    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
-        <v>2</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="12">
+        <f>C11</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <f>D11</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="14">
+        <f>E11</f>
+        <v>3.3145382505333738</v>
+      </c>
+      <c r="F29" s="14">
+        <f>F11</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G29" s="14">
+        <f t="shared" si="1"/>
+        <v>2.1046290831894328</v>
+      </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="12"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
-      <c r="B30" s="16" t="str">
-        <f>B10</f>
-        <v>-for road</v>
-      </c>
+      <c r="B30" s="16"/>
       <c r="C30" s="12">
-        <f>C10</f>
+        <f>C12</f>
         <v>1</v>
       </c>
       <c r="D30" s="14">
-        <f>D10</f>
+        <f>D12</f>
         <v>5</v>
       </c>
       <c r="E30" s="14">
-        <f>E10</f>
-        <v>3.3907345321548306</v>
+        <f>E12</f>
+        <v>3.0219445291069795</v>
       </c>
       <c r="F30" s="14">
-        <f>F10</f>
-        <v>0.12699380270242813</v>
+        <f>F12</f>
+        <v>0.10398760540485627</v>
       </c>
       <c r="G30" s="14">
-        <f t="shared" ref="G30:G45" si="1">PRODUCT(C30:F30)</f>
-        <v>2.1530113609639026</v>
+        <f t="shared" si="1"/>
+        <v>1.571223876240704</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
@@ -3629,24 +3695,24 @@
       <c r="A31" s="10"/>
       <c r="B31" s="16"/>
       <c r="C31" s="12">
-        <f t="shared" ref="C31:F45" si="2">C11</f>
+        <f>C13</f>
         <v>1</v>
       </c>
       <c r="D31" s="14">
-        <f t="shared" si="2"/>
+        <f>D13</f>
         <v>5</v>
       </c>
       <c r="E31" s="14">
-        <f t="shared" si="2"/>
-        <v>3.3145382505333738</v>
+        <f>E13</f>
+        <v>2.9838463882962509</v>
       </c>
       <c r="F31" s="14">
-        <f t="shared" si="2"/>
-        <v>0.12699380270242813</v>
+        <f>F13</f>
+        <v>0.11033729553997765</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="1"/>
-        <v>2.1046290831894328</v>
+        <v>1.6461477039566916</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
@@ -3657,24 +3723,24 @@
       <c r="A32" s="10"/>
       <c r="B32" s="16"/>
       <c r="C32" s="12">
-        <f t="shared" si="2"/>
+        <f>C14</f>
         <v>1</v>
       </c>
       <c r="D32" s="14">
-        <f t="shared" si="2"/>
+        <f>D14</f>
         <v>5</v>
       </c>
       <c r="E32" s="14">
-        <f t="shared" si="2"/>
-        <v>3.0219445291069795</v>
+        <f>E14</f>
+        <v>3.1621456872904599</v>
       </c>
       <c r="F32" s="14">
-        <f t="shared" si="2"/>
-        <v>0.10398760540485627</v>
+        <f>F14</f>
+        <v>0.11668698567509903</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="1"/>
-        <v>1.571223876240704</v>
+        <v>1.8449062425771903</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
@@ -3685,24 +3751,24 @@
       <c r="A33" s="10"/>
       <c r="B33" s="16"/>
       <c r="C33" s="12">
-        <f t="shared" si="2"/>
+        <f>C15</f>
         <v>1</v>
       </c>
       <c r="D33" s="14">
-        <f t="shared" si="2"/>
+        <f>D15</f>
         <v>5</v>
       </c>
       <c r="E33" s="14">
-        <f t="shared" si="2"/>
-        <v>2.9838463882962509</v>
+        <f>E15</f>
+        <v>3.0859494056690031</v>
       </c>
       <c r="F33" s="14">
-        <f t="shared" si="2"/>
-        <v>0.11033729553997765</v>
+        <f>F15</f>
+        <v>0.11668698567509903</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="1"/>
-        <v>1.6461477039566916</v>
+        <v>1.8004506704668966</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
@@ -3713,24 +3779,24 @@
       <c r="A34" s="10"/>
       <c r="B34" s="16"/>
       <c r="C34" s="12">
-        <f t="shared" si="2"/>
+        <f>C16</f>
         <v>1</v>
       </c>
       <c r="D34" s="14">
-        <f t="shared" si="2"/>
+        <f>D16</f>
         <v>5</v>
       </c>
       <c r="E34" s="14">
-        <f t="shared" si="2"/>
-        <v>3.1621456872904599</v>
+        <f>E16</f>
+        <v>3.1366961292288935</v>
       </c>
       <c r="F34" s="14">
-        <f t="shared" si="2"/>
-        <v>0.11668698567509903</v>
+        <f>F16</f>
+        <v>0.11033729553997765</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="1"/>
-        <v>1.8449062425771903</v>
+        <v>1.7304728391491617</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
@@ -3741,24 +3807,24 @@
       <c r="A35" s="10"/>
       <c r="B35" s="16"/>
       <c r="C35" s="12">
-        <f t="shared" si="2"/>
+        <f>C17</f>
         <v>1</v>
       </c>
       <c r="D35" s="14">
-        <f t="shared" si="2"/>
+        <f>D17</f>
         <v>5</v>
       </c>
       <c r="E35" s="14">
-        <f t="shared" si="2"/>
-        <v>3.0859494056690031</v>
+        <f>E17</f>
+        <v>3.1366961292288935</v>
       </c>
       <c r="F35" s="14">
-        <f t="shared" si="2"/>
-        <v>0.11668698567509903</v>
+        <f>F17</f>
+        <v>0.10398760540485627</v>
       </c>
       <c r="G35" s="14">
         <f t="shared" si="1"/>
-        <v>1.8004506704668966</v>
+        <v>1.6308875968059711</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
@@ -3769,24 +3835,24 @@
       <c r="A36" s="10"/>
       <c r="B36" s="16"/>
       <c r="C36" s="12">
-        <f t="shared" si="2"/>
+        <f>C18</f>
         <v>1</v>
       </c>
       <c r="D36" s="14">
-        <f t="shared" si="2"/>
+        <f>D18</f>
         <v>5</v>
       </c>
       <c r="E36" s="14">
-        <f t="shared" si="2"/>
-        <v>3.1366961292288935</v>
+        <f>E18</f>
+        <v>3.1240475464797317</v>
       </c>
       <c r="F36" s="14">
-        <f t="shared" si="2"/>
-        <v>0.11033729553997765</v>
+        <f>F18</f>
+        <v>0.10398760540485627</v>
       </c>
       <c r="G36" s="14">
         <f t="shared" si="1"/>
-        <v>1.7304728391491617</v>
+        <v>1.6243111176467186</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
@@ -3797,24 +3863,24 @@
       <c r="A37" s="10"/>
       <c r="B37" s="16"/>
       <c r="C37" s="12">
-        <f t="shared" si="2"/>
+        <f>C19</f>
         <v>1</v>
       </c>
       <c r="D37" s="14">
-        <f t="shared" si="2"/>
+        <f>D19</f>
         <v>5</v>
       </c>
       <c r="E37" s="14">
-        <f t="shared" si="2"/>
-        <v>3.1366961292288935</v>
+        <f>E19</f>
+        <v>3.2002438281011885</v>
       </c>
       <c r="F37" s="14">
-        <f t="shared" si="2"/>
+        <f>F19</f>
         <v>0.10398760540485627</v>
       </c>
       <c r="G37" s="14">
         <f t="shared" si="1"/>
-        <v>1.6308875968059711</v>
+        <v>1.6639284619795653</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
@@ -3825,24 +3891,24 @@
       <c r="A38" s="10"/>
       <c r="B38" s="16"/>
       <c r="C38" s="12">
-        <f t="shared" si="2"/>
+        <f>C20</f>
         <v>1</v>
       </c>
       <c r="D38" s="14">
-        <f t="shared" si="2"/>
+        <f>D20</f>
         <v>5</v>
       </c>
       <c r="E38" s="14">
-        <f t="shared" si="2"/>
+        <f>E20</f>
         <v>3.1240475464797317</v>
       </c>
       <c r="F38" s="14">
-        <f t="shared" si="2"/>
-        <v>0.10398760540485627</v>
+        <f>F20</f>
+        <v>7.8588844864370622E-2</v>
       </c>
       <c r="G38" s="14">
         <f t="shared" si="1"/>
-        <v>1.6243111176467186</v>
+        <v>1.2275764398960665</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
@@ -3853,135 +3919,98 @@
       <c r="A39" s="10"/>
       <c r="B39" s="16"/>
       <c r="C39" s="12">
-        <f t="shared" si="2"/>
+        <f>C21</f>
         <v>1</v>
       </c>
       <c r="D39" s="14">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>D21</f>
+        <v>3.047851264858275</v>
       </c>
       <c r="E39" s="14">
-        <f t="shared" si="2"/>
+        <f>E21</f>
         <v>3.2002438281011885</v>
       </c>
       <c r="F39" s="14">
-        <f t="shared" si="2"/>
-        <v>0.10398760540485627</v>
+        <f>F21</f>
+        <v>6.5889464594127783E-2</v>
       </c>
       <c r="G39" s="14">
         <f t="shared" si="1"/>
-        <v>1.6639284619795653</v>
+        <v>0.64267708748628227</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="13"/>
       <c r="K39" s="12"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D40" s="14">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="E40" s="14">
-        <f t="shared" si="2"/>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="F40" s="14">
-        <f t="shared" si="2"/>
-        <v>7.8588844864370622E-2</v>
-      </c>
-      <c r="G40" s="14">
-        <f t="shared" si="1"/>
-        <v>1.2275764398960665</v>
-      </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="12"/>
+    <row r="40" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19">
+        <f>SUM(G28:G39)</f>
+        <v>19.640222480358585</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="2">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J40" s="19">
+        <f>G40*I40</f>
+        <v>87566.324733128364</v>
+      </c>
+      <c r="K40" s="18"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D41" s="14">
-        <f t="shared" si="2"/>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E41" s="14">
-        <f t="shared" si="2"/>
-        <v>3.2002438281011885</v>
-      </c>
-      <c r="F41" s="14">
-        <f t="shared" si="2"/>
-        <v>6.5889464594127783E-2</v>
-      </c>
-      <c r="G41" s="14">
-        <f t="shared" si="1"/>
-        <v>0.64267708748628227</v>
-      </c>
+      <c r="B41" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
+      <c r="J41" s="13">
+        <f>0.13*G40*14817.6/5</f>
+        <v>7566.544976248997</v>
+      </c>
       <c r="K41" s="12"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="12">
-        <v>0</v>
-      </c>
-      <c r="D42" s="14">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="E42" s="14">
-        <f t="shared" si="2"/>
-        <v>3.5557756781469063</v>
-      </c>
-      <c r="F42" s="14">
-        <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="G42" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
-      <c r="J42" s="13"/>
+      <c r="J42" s="12"/>
       <c r="K42" s="12"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="12">
-        <v>0</v>
-      </c>
-      <c r="D43" s="14">
-        <f t="shared" si="2"/>
-        <v>0.35558264756679875</v>
-      </c>
-      <c r="E43" s="14">
-        <f t="shared" si="2"/>
-        <v>3.8351112465711674</v>
-      </c>
-      <c r="F43" s="14">
-        <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="G43" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="43" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>3</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="12"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
       <c r="J43" s="13"/>
@@ -3989,25 +4018,28 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="16"/>
+      <c r="B44" s="16" t="str">
+        <f>B28</f>
+        <v>-for road</v>
+      </c>
       <c r="C44" s="12">
-        <v>0</v>
+        <f>C10</f>
+        <v>1</v>
       </c>
       <c r="D44" s="14">
-        <f t="shared" si="2"/>
+        <f>D10</f>
         <v>5</v>
       </c>
       <c r="E44" s="14">
-        <f t="shared" si="2"/>
-        <v>4.4925556232855843</v>
-      </c>
-      <c r="F44" s="14">
-        <f t="shared" si="2"/>
+        <f>E10</f>
+        <v>3.3907345321548306</v>
+      </c>
+      <c r="F44" s="12">
         <v>0.15</v>
       </c>
       <c r="G44" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="G44:G57" si="2">PRODUCT(C44:F44)</f>
+        <v>2.5430508991161229</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
@@ -4018,97 +4050,132 @@
       <c r="A45" s="10"/>
       <c r="B45" s="16"/>
       <c r="C45" s="12">
-        <v>0</v>
+        <f>C11</f>
+        <v>1</v>
       </c>
       <c r="D45" s="14">
+        <f>D11</f>
+        <v>5</v>
+      </c>
+      <c r="E45" s="14">
+        <f>E11</f>
+        <v>3.3145382505333738</v>
+      </c>
+      <c r="F45" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G45" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E45" s="14">
-        <f t="shared" si="2"/>
-        <v>5.6750000000000007</v>
-      </c>
-      <c r="F45" s="14">
-        <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="G45" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.4859036879000302</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
       <c r="J45" s="13"/>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="19">
-        <f>SUM(G30:G45)</f>
-        <v>19.640222480358585</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I46" s="2">
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="J46" s="19">
-        <f>G46*I46</f>
-        <v>87566.324733128364</v>
-      </c>
-      <c r="K46" s="18"/>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="10"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="12">
+        <f>C12</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="14">
+        <f>D12</f>
+        <v>5</v>
+      </c>
+      <c r="E46" s="14">
+        <f>E12</f>
+        <v>3.0219445291069795</v>
+      </c>
+      <c r="F46" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G46" s="14">
+        <f t="shared" si="2"/>
+        <v>2.2664583968302345</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="12"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="12">
+        <f>C13</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="14">
+        <f>D13</f>
+        <v>5</v>
+      </c>
+      <c r="E47" s="14">
+        <f>E13</f>
+        <v>2.9838463882962509</v>
+      </c>
+      <c r="F47" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G47" s="14">
+        <f t="shared" si="2"/>
+        <v>2.237884791222188</v>
+      </c>
       <c r="H47" s="12"/>
       <c r="I47" s="12"/>
-      <c r="J47" s="13">
-        <f>0.13*G46*14817.6/5</f>
-        <v>7566.544976248997</v>
-      </c>
+      <c r="J47" s="13"/>
       <c r="K47" s="12"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="12">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D48" s="14">
+        <f>D14</f>
+        <v>5</v>
+      </c>
+      <c r="E48" s="14">
+        <f>E14</f>
+        <v>3.1621456872904599</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0.125</v>
+      </c>
+      <c r="G48" s="14">
+        <f t="shared" si="2"/>
+        <v>1.9763410545565374</v>
+      </c>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
+      <c r="J48" s="13"/>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
-        <v>3</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="12"/>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="10"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="12">
+        <f>C15</f>
+        <v>1</v>
+      </c>
+      <c r="D49" s="14">
+        <f>D15</f>
+        <v>5</v>
+      </c>
+      <c r="E49" s="14">
+        <f>E15</f>
+        <v>3.0859494056690031</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G49" s="14">
+        <f t="shared" si="2"/>
+        <v>2.3144620542517522</v>
+      </c>
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
       <c r="J49" s="13"/>
@@ -4116,33 +4183,28 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="16" t="str">
-        <f>B30</f>
-        <v>-for road</v>
-      </c>
+      <c r="B50" s="16"/>
       <c r="C50" s="12">
-        <f>C10</f>
+        <f>C16</f>
         <v>1</v>
       </c>
       <c r="D50" s="14">
-        <f t="shared" ref="D50:F50" si="3">D10</f>
+        <f>D16</f>
         <v>5</v>
       </c>
       <c r="E50" s="14">
-        <f t="shared" si="3"/>
-        <v>3.3907345321548306</v>
+        <f>E16</f>
+        <v>3.1366961292288935</v>
       </c>
       <c r="F50" s="12">
         <v>0.15</v>
       </c>
       <c r="G50" s="14">
-        <f t="shared" ref="G50:G65" si="4">PRODUCT(C50:F50)</f>
-        <v>2.5430508991161229</v>
+        <f t="shared" si="2"/>
+        <v>2.3525220969216698</v>
       </c>
       <c r="H50" s="12"/>
-      <c r="I50" s="12">
-        <v>0.15</v>
-      </c>
+      <c r="I50" s="12"/>
       <c r="J50" s="13"/>
       <c r="K50" s="12"/>
     </row>
@@ -4150,23 +4212,23 @@
       <c r="A51" s="10"/>
       <c r="B51" s="16"/>
       <c r="C51" s="12">
-        <f t="shared" ref="C51:F51" si="5">C11</f>
+        <f>C17</f>
         <v>1</v>
       </c>
       <c r="D51" s="14">
-        <f t="shared" si="5"/>
+        <f>D17</f>
         <v>5</v>
       </c>
       <c r="E51" s="14">
-        <f t="shared" si="5"/>
-        <v>3.3145382505333738</v>
+        <f>E17</f>
+        <v>3.1366961292288935</v>
       </c>
       <c r="F51" s="12">
         <v>0.15</v>
       </c>
       <c r="G51" s="14">
-        <f t="shared" si="4"/>
-        <v>2.4859036879000302</v>
+        <f t="shared" si="2"/>
+        <v>2.3525220969216698</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
@@ -4177,23 +4239,23 @@
       <c r="A52" s="10"/>
       <c r="B52" s="16"/>
       <c r="C52" s="12">
-        <f t="shared" ref="C52:F52" si="6">C12</f>
+        <f>C18</f>
         <v>1</v>
       </c>
       <c r="D52" s="14">
-        <f t="shared" si="6"/>
+        <f>D18</f>
         <v>5</v>
       </c>
       <c r="E52" s="14">
-        <f t="shared" si="6"/>
-        <v>3.0219445291069795</v>
-      </c>
-      <c r="F52" s="12">
-        <v>0.15</v>
+        <f>E18</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0.125</v>
       </c>
       <c r="G52" s="14">
-        <f t="shared" si="4"/>
-        <v>2.2664583968302345</v>
+        <f t="shared" si="2"/>
+        <v>1.9525297165498323</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
@@ -4204,23 +4266,24 @@
       <c r="A53" s="10"/>
       <c r="B53" s="16"/>
       <c r="C53" s="12">
-        <f t="shared" ref="C53:F53" si="7">C13</f>
+        <f>C19</f>
         <v>1</v>
       </c>
       <c r="D53" s="14">
-        <f t="shared" si="7"/>
+        <f>D19</f>
         <v>5</v>
       </c>
       <c r="E53" s="14">
-        <f t="shared" si="7"/>
-        <v>2.9838463882962509</v>
-      </c>
-      <c r="F53" s="12">
-        <v>0.15</v>
+        <f>E19</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F53" s="14">
+        <f>F37</f>
+        <v>0.10398760540485627</v>
       </c>
       <c r="G53" s="14">
-        <f t="shared" si="4"/>
-        <v>2.237884791222188</v>
+        <f t="shared" si="2"/>
+        <v>1.6639284619795653</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
@@ -4231,23 +4294,23 @@
       <c r="A54" s="10"/>
       <c r="B54" s="16"/>
       <c r="C54" s="12">
-        <f t="shared" ref="C54:F54" si="8">C14</f>
+        <f>C20</f>
         <v>1</v>
       </c>
       <c r="D54" s="14">
-        <f t="shared" si="8"/>
+        <f>D20</f>
         <v>5</v>
       </c>
       <c r="E54" s="14">
-        <f t="shared" si="8"/>
-        <v>3.1621456872904599</v>
-      </c>
-      <c r="F54" s="12">
-        <v>0.15</v>
+        <f>E20</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0.1</v>
       </c>
       <c r="G54" s="14">
-        <f t="shared" si="4"/>
-        <v>2.3716092654678449</v>
+        <f t="shared" si="2"/>
+        <v>1.5620237732398659</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
@@ -4258,23 +4321,23 @@
       <c r="A55" s="10"/>
       <c r="B55" s="16"/>
       <c r="C55" s="12">
-        <f t="shared" ref="C55:F55" si="9">C15</f>
+        <f>C21</f>
         <v>1</v>
       </c>
       <c r="D55" s="14">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f>D21</f>
+        <v>3.047851264858275</v>
       </c>
       <c r="E55" s="14">
-        <f t="shared" si="9"/>
-        <v>3.0859494056690031</v>
-      </c>
-      <c r="F55" s="12">
-        <v>0.15</v>
+        <f>E21</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0.1</v>
       </c>
       <c r="G55" s="14">
-        <f t="shared" si="4"/>
-        <v>2.3144620542517522</v>
+        <f t="shared" si="2"/>
+        <v>0.97538671993330961</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
@@ -4285,23 +4348,24 @@
       <c r="A56" s="10"/>
       <c r="B56" s="16"/>
       <c r="C56" s="12">
-        <f t="shared" ref="C56:F56" si="10">C16</f>
+        <f>C22</f>
         <v>1</v>
       </c>
       <c r="D56" s="14">
-        <f t="shared" si="10"/>
+        <f>D22</f>
         <v>5</v>
       </c>
       <c r="E56" s="14">
-        <f t="shared" si="10"/>
-        <v>3.1366961292288935</v>
-      </c>
-      <c r="F56" s="12">
+        <f>E22</f>
+        <v>3.5557756781469063</v>
+      </c>
+      <c r="F56" s="14">
+        <f>F22</f>
         <v>0.15</v>
       </c>
       <c r="G56" s="14">
-        <f t="shared" si="4"/>
-        <v>2.3525220969216698</v>
+        <f t="shared" si="2"/>
+        <v>2.6668317586101797</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
@@ -4312,485 +4376,567 @@
       <c r="A57" s="10"/>
       <c r="B57" s="16"/>
       <c r="C57" s="12">
-        <f t="shared" ref="C57:F57" si="11">C17</f>
+        <f>C23</f>
         <v>1</v>
       </c>
       <c r="D57" s="14">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f>D23</f>
+        <v>0.35558264756679875</v>
       </c>
       <c r="E57" s="14">
-        <f t="shared" si="11"/>
-        <v>3.1366961292288935</v>
-      </c>
-      <c r="F57" s="12">
+        <f>E23</f>
+        <v>3.8351112465711674</v>
+      </c>
+      <c r="F57" s="14">
+        <f>F23</f>
         <v>0.15</v>
       </c>
       <c r="G57" s="14">
-        <f t="shared" si="4"/>
-        <v>2.3525220969216698</v>
+        <f t="shared" si="2"/>
+        <v>0.20455485161534726</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
       <c r="J57" s="13"/>
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="12">
-        <f t="shared" ref="C58:F58" si="12">C18</f>
-        <v>1</v>
-      </c>
-      <c r="D58" s="14">
-        <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="E58" s="14">
-        <f t="shared" si="12"/>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="F58" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="G58" s="14">
-        <f t="shared" si="4"/>
-        <v>2.3430356598597988</v>
-      </c>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="12"/>
+    <row r="58" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="17"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="19">
+        <f>SUM(G44:G57)</f>
+        <v>27.554400359648305</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="2">
+        <v>12000.5</v>
+      </c>
+      <c r="J58" s="19">
+        <f>G58*I58</f>
+        <v>330666.58151595946</v>
+      </c>
+      <c r="K58" s="18"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="12">
-        <f t="shared" ref="C59:F59" si="13">C19</f>
-        <v>1</v>
-      </c>
-      <c r="D59" s="14">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="E59" s="14">
-        <f t="shared" si="13"/>
-        <v>3.2002438281011885</v>
-      </c>
-      <c r="F59" s="14">
-        <f>F39</f>
-        <v>0.10398760540485627</v>
-      </c>
-      <c r="G59" s="14">
-        <f t="shared" si="4"/>
-        <v>1.6639284619795653</v>
-      </c>
+      <c r="B59" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
-      <c r="J59" s="13"/>
+      <c r="J59" s="13">
+        <f>0.13*G58*67891.51/15</f>
+        <v>16212.818678862574</v>
+      </c>
       <c r="K59" s="12"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="12">
-        <f t="shared" ref="C60:F60" si="14">C20</f>
-        <v>1</v>
-      </c>
-      <c r="D60" s="14">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="E60" s="14">
-        <f t="shared" si="14"/>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="F60" s="14">
-        <f t="shared" si="14"/>
-        <v>7.8588844864370622E-2</v>
-      </c>
-      <c r="G60" s="14">
-        <f t="shared" si="4"/>
-        <v>1.2275764398960665</v>
-      </c>
+      <c r="B60" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
-      <c r="J60" s="13"/>
+      <c r="J60" s="13">
+        <f>0.13*G58*21432.6/15</f>
+        <v>5118.2078232843842</v>
+      </c>
       <c r="K60" s="12"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="12">
-        <f t="shared" ref="C61:F61" si="15">C21</f>
-        <v>1</v>
-      </c>
-      <c r="D61" s="14">
-        <f t="shared" si="15"/>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E61" s="14">
-        <f t="shared" si="15"/>
-        <v>3.2002438281011885</v>
-      </c>
-      <c r="F61" s="14">
-        <f t="shared" si="15"/>
-        <v>6.5889464594127783E-2</v>
-      </c>
-      <c r="G61" s="14">
-        <f t="shared" si="4"/>
-        <v>0.64267708748628227</v>
-      </c>
+      <c r="B61" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
-      <c r="J61" s="13"/>
+      <c r="J61" s="13">
+        <f>0.13*G58*(27147.96+17146.08)/15</f>
+        <v>10577.629501454396</v>
+      </c>
       <c r="K61" s="12"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="12">
-        <f t="shared" ref="C62:F62" si="16">C22</f>
-        <v>1</v>
-      </c>
-      <c r="D62" s="14">
-        <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="E62" s="14">
-        <f t="shared" si="16"/>
-        <v>3.5557756781469063</v>
-      </c>
-      <c r="F62" s="14">
-        <f t="shared" si="16"/>
-        <v>0.15</v>
-      </c>
-      <c r="G62" s="14">
-        <f t="shared" si="4"/>
-        <v>2.6668317586101797</v>
-      </c>
+      <c r="B62" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
-      <c r="J62" s="13"/>
+      <c r="J62" s="13">
+        <f>0.13*G58*775/15</f>
+        <v>185.07372241563777</v>
+      </c>
       <c r="K62" s="12"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="12">
-        <f t="shared" ref="C63:F63" si="17">C23</f>
-        <v>1</v>
-      </c>
-      <c r="D63" s="14">
-        <f t="shared" si="17"/>
-        <v>0.35558264756679875</v>
-      </c>
-      <c r="E63" s="14">
-        <f t="shared" si="17"/>
-        <v>3.8351112465711674</v>
-      </c>
-      <c r="F63" s="14">
-        <f t="shared" si="17"/>
-        <v>0.15</v>
-      </c>
-      <c r="G63" s="14">
-        <f t="shared" si="4"/>
-        <v>0.20455485161534726</v>
-      </c>
+      <c r="B63" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="13"/>
+      <c r="J63" s="13">
+        <f>0.13*G58*6923.4/15</f>
+        <v>1653.3411738999052</v>
+      </c>
       <c r="K63" s="12"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="12">
-        <f t="shared" ref="C64:F64" si="18">C24</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="14">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="E64" s="14">
-        <f t="shared" si="18"/>
-        <v>4.4925556232855843</v>
-      </c>
-      <c r="F64" s="14">
-        <f t="shared" si="18"/>
-        <v>0.15</v>
-      </c>
-      <c r="G64" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="B64" s="22"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
       <c r="J64" s="13"/>
       <c r="K64" s="12"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="10"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="12">
-        <f t="shared" ref="C65:F65" si="19">C25</f>
+    <row r="65" spans="1:16" s="21" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>4</v>
+      </c>
+      <c r="B65" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="32"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="10"/>
+      <c r="B66" s="16" t="str">
+        <f>B10</f>
+        <v>-for road</v>
+      </c>
+      <c r="C66" s="12">
+        <v>16</v>
+      </c>
+      <c r="D66" s="14">
+        <v>4</v>
+      </c>
+      <c r="E66" s="14">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F66" s="94">
+        <f>PRODUCT(C66:E66)</f>
+        <v>25.283950617283949</v>
+      </c>
+      <c r="G66" s="94">
+        <f>F66/1000</f>
+        <v>2.5283950617283949E-2</v>
+      </c>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="12"/>
+      <c r="M66" s="3">
+        <f>D67/(7/12/3.281)</f>
+        <v>16.311257142857141</v>
+      </c>
+      <c r="N66" s="3">
+        <f>TRUNC(M66,0)</f>
+        <v>16</v>
+      </c>
+      <c r="O66" s="3">
+        <f>C66-N66</f>
         <v>0</v>
       </c>
-      <c r="D65" s="14">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="E65" s="14">
-        <f t="shared" si="19"/>
-        <v>5.6750000000000007</v>
-      </c>
-      <c r="F65" s="14">
-        <f t="shared" si="19"/>
-        <v>0.15</v>
-      </c>
-      <c r="G65" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="12"/>
-    </row>
-    <row r="66" spans="1:16" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="15"/>
-      <c r="B66" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C66" s="17"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="19">
-        <f>SUM(G50:G65)</f>
-        <v>27.673017548078754</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I66" s="2">
-        <v>12000.5</v>
-      </c>
-      <c r="J66" s="19">
-        <f>G66*I66</f>
-        <v>332090.04708571907</v>
-      </c>
-      <c r="K66" s="18"/>
+      <c r="P66" s="47"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
-      <c r="B67" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="12">
+        <v>22</v>
+      </c>
+      <c r="D67" s="14">
+        <v>2.9</v>
+      </c>
+      <c r="E67" s="14">
+        <f t="shared" ref="E67:E93" si="3">8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F67" s="94">
+        <f t="shared" ref="F67:F93" si="4">PRODUCT(C67:E67)</f>
+        <v>25.204938271604934</v>
+      </c>
+      <c r="G67" s="94">
+        <f t="shared" ref="G67:G93" si="5">F67/1000</f>
+        <v>2.5204938271604936E-2</v>
+      </c>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="13">
-        <f>0.13*G66*67891.51/15</f>
-        <v>16282.612212494889</v>
-      </c>
+      <c r="J67" s="13"/>
       <c r="K67" s="12"/>
+      <c r="M67" s="3">
+        <f>D66/(7/12/3.281)</f>
+        <v>22.498285714285714</v>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" ref="N67:N93" si="6">TRUNC(M67,0)</f>
+        <v>22</v>
+      </c>
+      <c r="O67" s="3">
+        <f t="shared" ref="O67:O93" si="7">C67-N67</f>
+        <v>0</v>
+      </c>
+      <c r="P67" s="47"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="10"/>
-      <c r="B68" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="12">
+        <v>16</v>
+      </c>
+      <c r="D68" s="14">
+        <v>4.12</v>
+      </c>
+      <c r="E68" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F68" s="94">
+        <f t="shared" si="4"/>
+        <v>26.042469135802467</v>
+      </c>
+      <c r="G68" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6042469135802465E-2</v>
+      </c>
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
-      <c r="J68" s="13">
-        <f>0.13*G66*21432.6/15</f>
-        <v>5140.2408711415901</v>
-      </c>
+      <c r="J68" s="13"/>
       <c r="K68" s="12"/>
+      <c r="M68" s="3">
+        <f t="shared" ref="M68" si="8">D69/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O68" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
-      <c r="B69" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="12">
+        <v>23</v>
+      </c>
+      <c r="D69" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E69" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F69" s="94">
+        <f t="shared" si="4"/>
+        <v>26.714074074074073</v>
+      </c>
+      <c r="G69" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6714074074074074E-2</v>
+      </c>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="13">
-        <f>0.13*G66*(27147.96+17146.08)/15</f>
-        <v>10623.164467025954</v>
-      </c>
+      <c r="J69" s="13"/>
       <c r="K69" s="12"/>
+      <c r="M69" s="3">
+        <f t="shared" ref="M69" si="9">D68/(7/12/3.281)</f>
+        <v>23.173234285714287</v>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O69" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="10"/>
-      <c r="B70" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="12">
+        <v>16</v>
+      </c>
+      <c r="D70" s="14">
+        <v>3.9</v>
+      </c>
+      <c r="E70" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F70" s="94">
+        <f t="shared" si="4"/>
+        <v>24.651851851851848</v>
+      </c>
+      <c r="G70" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4651851851851848E-2</v>
+      </c>
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
-      <c r="J70" s="13">
-        <f>0.13*G66*775/15</f>
-        <v>185.8704345312623</v>
-      </c>
+      <c r="J70" s="13"/>
       <c r="K70" s="12"/>
+      <c r="M70" s="3">
+        <f t="shared" ref="M70" si="10">D71/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N70" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O70" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
-      <c r="B71" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="12">
+        <v>21</v>
+      </c>
+      <c r="D71" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E71" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F71" s="94">
+        <f t="shared" si="4"/>
+        <v>24.391111111111112</v>
+      </c>
+      <c r="G71" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4391111111111113E-2</v>
+      </c>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="13">
-        <f>0.13*G66*6923.4/15</f>
-        <v>1660.4585373338598</v>
-      </c>
+      <c r="J71" s="13"/>
       <c r="K71" s="12"/>
+      <c r="M71" s="3">
+        <f t="shared" ref="M71" si="11">D70/(7/12/3.281)</f>
+        <v>21.935828571428569</v>
+      </c>
+      <c r="N71" s="3">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="O71" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="10"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="12">
+        <v>15</v>
+      </c>
+      <c r="D72" s="14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E72" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F72" s="94">
+        <f t="shared" si="4"/>
+        <v>30.222222222222221</v>
+      </c>
+      <c r="G72" s="94">
+        <f t="shared" si="5"/>
+        <v>3.022222222222222E-2</v>
+      </c>
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
       <c r="J72" s="13"/>
       <c r="K72" s="12"/>
-    </row>
-    <row r="73" spans="1:16" s="21" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
-        <v>4</v>
-      </c>
-      <c r="B73" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="E73" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="F73" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="32"/>
+      <c r="M72" s="3">
+        <f t="shared" ref="M72" si="12">D73/(7/12/3.281)</f>
+        <v>15.186342857142858</v>
+      </c>
+      <c r="N72" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="O72" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="10"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="12">
+        <v>28</v>
+      </c>
+      <c r="D73" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="E73" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F73" s="94">
+        <f t="shared" si="4"/>
+        <v>29.866666666666667</v>
+      </c>
+      <c r="G73" s="94">
+        <f t="shared" si="5"/>
+        <v>2.9866666666666666E-2</v>
+      </c>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="12"/>
+      <c r="M73" s="3">
+        <f t="shared" ref="M73" si="13">D72/(7/12/3.281)</f>
+        <v>28.685314285714284</v>
+      </c>
+      <c r="N73" s="3">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="O73" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="10"/>
-      <c r="B74" s="16" t="str">
-        <f>B10</f>
-        <v>-for road</v>
-      </c>
+      <c r="B74" s="16"/>
       <c r="C74" s="12">
         <v>16</v>
       </c>
       <c r="D74" s="14">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="E74" s="14">
-        <f>8*8/162</f>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F74" s="12">
-        <f>PRODUCT(C74:E74)</f>
-        <v>25.283950617283949</v>
-      </c>
-      <c r="G74" s="14">
-        <f>F74/1000</f>
-        <v>2.5283950617283949E-2</v>
+      <c r="F74" s="94">
+        <f t="shared" si="4"/>
+        <v>24.46222222222222</v>
+      </c>
+      <c r="G74" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4462222222222219E-2</v>
       </c>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
       <c r="J74" s="13"/>
       <c r="K74" s="12"/>
       <c r="M74" s="3">
-        <f>D75/(7/12/3.281)</f>
-        <v>16.311257142857141</v>
+        <f t="shared" ref="M74" si="14">D75/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
       </c>
       <c r="N74" s="3">
-        <f>TRUNC(M74,0)</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O74" s="3">
-        <f>C74-N74</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P74" s="47"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="10"/>
       <c r="B75" s="16"/>
       <c r="C75" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D75" s="14">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="E75" s="14">
-        <f t="shared" ref="E75:E101" si="20">8*8/162</f>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F75" s="12">
-        <f t="shared" ref="F75:F101" si="21">PRODUCT(C75:E75)</f>
-        <v>25.204938271604934</v>
-      </c>
-      <c r="G75" s="14">
-        <f t="shared" ref="G75:G101" si="22">F75/1000</f>
-        <v>2.5204938271604936E-2</v>
+      <c r="F75" s="94">
+        <f t="shared" si="4"/>
+        <v>24.391111111111112</v>
+      </c>
+      <c r="G75" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4391111111111113E-2</v>
       </c>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="13"/>
       <c r="K75" s="12"/>
       <c r="M75" s="3">
-        <f>D74/(7/12/3.281)</f>
-        <v>22.498285714285714</v>
+        <f t="shared" ref="M75" si="15">D74/(7/12/3.281)</f>
+        <v>21.76709142857143</v>
       </c>
       <c r="N75" s="3">
-        <f t="shared" ref="N75:N101" si="23">TRUNC(M75,0)</f>
-        <v>22</v>
+        <f t="shared" si="6"/>
+        <v>21</v>
       </c>
       <c r="O75" s="3">
-        <f t="shared" ref="O75:O101" si="24">C75-N75</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P75" s="47"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="10"/>
@@ -4799,34 +4945,34 @@
         <v>16</v>
       </c>
       <c r="D76" s="14">
-        <v>4.12</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E76" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F76" s="12">
-        <f t="shared" si="21"/>
-        <v>26.042469135802467</v>
-      </c>
-      <c r="G76" s="14">
-        <f t="shared" si="22"/>
-        <v>2.6042469135802465E-2</v>
+      <c r="F76" s="94">
+        <f t="shared" si="4"/>
+        <v>25.663209876543206</v>
+      </c>
+      <c r="G76" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5663209876543205E-2</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
       <c r="J76" s="13"/>
       <c r="K76" s="12"/>
       <c r="M76" s="3">
-        <f t="shared" ref="M76" si="25">D77/(7/12/3.281)</f>
-        <v>16.536239999999999</v>
+        <f t="shared" ref="M76" si="16">D77/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
       </c>
       <c r="N76" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O76" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4834,37 +4980,37 @@
       <c r="A77" s="10"/>
       <c r="B77" s="16"/>
       <c r="C77" s="12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D77" s="14">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="E77" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F77" s="12">
-        <f t="shared" si="21"/>
-        <v>26.714074074074073</v>
-      </c>
-      <c r="G77" s="14">
-        <f t="shared" si="22"/>
-        <v>2.6714074074074074E-2</v>
+      <c r="F77" s="94">
+        <f t="shared" si="4"/>
+        <v>25.465679012345682</v>
+      </c>
+      <c r="G77" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5465679012345682E-2</v>
       </c>
       <c r="H77" s="12"/>
       <c r="I77" s="12"/>
       <c r="J77" s="13"/>
       <c r="K77" s="12"/>
       <c r="M77" s="3">
-        <f t="shared" ref="M77" si="26">D76/(7/12/3.281)</f>
-        <v>23.173234285714287</v>
+        <f t="shared" ref="M77" si="17">D76/(7/12/3.281)</f>
+        <v>22.835759999999997</v>
       </c>
       <c r="N77" s="3">
-        <f t="shared" si="23"/>
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="O77" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4875,34 +5021,34 @@
         <v>16</v>
       </c>
       <c r="D78" s="14">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E78" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F78" s="12">
-        <f t="shared" si="21"/>
-        <v>24.651851851851848</v>
-      </c>
-      <c r="G78" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4651851851851848E-2</v>
+      <c r="F78" s="94">
+        <f t="shared" si="4"/>
+        <v>25.916049382716047</v>
+      </c>
+      <c r="G78" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5916049382716046E-2</v>
       </c>
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
       <c r="J78" s="13"/>
       <c r="K78" s="12"/>
       <c r="M78" s="3">
-        <f t="shared" ref="M78" si="27">D79/(7/12/3.281)</f>
+        <f t="shared" ref="M78" si="18">D79/(7/12/3.281)</f>
         <v>16.536239999999999</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4910,37 +5056,37 @@
       <c r="A79" s="10"/>
       <c r="B79" s="16"/>
       <c r="C79" s="12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D79" s="14">
         <v>2.94</v>
       </c>
       <c r="E79" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F79" s="12">
-        <f t="shared" si="21"/>
-        <v>24.391111111111112</v>
-      </c>
-      <c r="G79" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4391111111111113E-2</v>
+      <c r="F79" s="94">
+        <f t="shared" si="4"/>
+        <v>26.714074074074073</v>
+      </c>
+      <c r="G79" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6714074074074074E-2</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
       <c r="J79" s="13"/>
       <c r="K79" s="12"/>
       <c r="M79" s="3">
-        <f t="shared" ref="M79" si="28">D78/(7/12/3.281)</f>
-        <v>21.935828571428569</v>
+        <f t="shared" ref="M79" si="19">D78/(7/12/3.281)</f>
+        <v>23.060742857142856</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="23"/>
-        <v>21</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4951,34 +5097,34 @@
         <v>15</v>
       </c>
       <c r="D80" s="14">
-        <v>5.0999999999999996</v>
+        <v>4.13</v>
       </c>
       <c r="E80" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F80" s="12">
-        <f t="shared" si="21"/>
-        <v>30.222222222222221</v>
-      </c>
-      <c r="G80" s="14">
-        <f t="shared" si="22"/>
-        <v>3.022222222222222E-2</v>
+      <c r="F80" s="94">
+        <f t="shared" si="4"/>
+        <v>24.474074074074071</v>
+      </c>
+      <c r="G80" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4474074074074072E-2</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
       <c r="J80" s="13"/>
       <c r="K80" s="12"/>
       <c r="M80" s="3">
-        <f t="shared" ref="M80" si="29">D81/(7/12/3.281)</f>
+        <f t="shared" ref="M80" si="20">D81/(7/12/3.281)</f>
         <v>15.186342857142858</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4986,37 +5132,37 @@
       <c r="A81" s="10"/>
       <c r="B81" s="16"/>
       <c r="C81" s="12">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D81" s="14">
         <v>2.7</v>
       </c>
       <c r="E81" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F81" s="12">
-        <f t="shared" si="21"/>
-        <v>29.866666666666667</v>
-      </c>
-      <c r="G81" s="14">
-        <f t="shared" si="22"/>
-        <v>2.9866666666666666E-2</v>
+      <c r="F81" s="94">
+        <f t="shared" si="4"/>
+        <v>24.533333333333331</v>
+      </c>
+      <c r="G81" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4533333333333331E-2</v>
       </c>
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
       <c r="J81" s="13"/>
       <c r="K81" s="12"/>
       <c r="M81" s="3">
-        <f t="shared" ref="M81" si="30">D80/(7/12/3.281)</f>
-        <v>28.685314285714284</v>
+        <f t="shared" ref="M81" si="21">D80/(7/12/3.281)</f>
+        <v>23.229479999999999</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="23"/>
-        <v>28</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5027,34 +5173,34 @@
         <v>16</v>
       </c>
       <c r="D82" s="14">
-        <v>3.87</v>
+        <v>2.82</v>
       </c>
       <c r="E82" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F82" s="12">
-        <f t="shared" si="21"/>
-        <v>24.46222222222222</v>
-      </c>
-      <c r="G82" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4462222222222219E-2</v>
+      <c r="F82" s="94">
+        <f t="shared" si="4"/>
+        <v>17.825185185185184</v>
+      </c>
+      <c r="G82" s="94">
+        <f t="shared" si="5"/>
+        <v>1.7825185185185183E-2</v>
       </c>
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
       <c r="J82" s="13"/>
       <c r="K82" s="12"/>
       <c r="M82" s="3">
-        <f t="shared" ref="M82" si="31">D83/(7/12/3.281)</f>
-        <v>16.536239999999999</v>
+        <f t="shared" ref="M82" si="22">D83/(7/12/3.281)</f>
+        <v>16.704977142857143</v>
       </c>
       <c r="N82" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O82" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5062,37 +5208,37 @@
       <c r="A83" s="10"/>
       <c r="B83" s="16"/>
       <c r="C83" s="12">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D83" s="14">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="E83" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F83" s="12">
-        <f t="shared" si="21"/>
-        <v>24.391111111111112</v>
-      </c>
-      <c r="G83" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4391111111111113E-2</v>
+      <c r="F83" s="94">
+        <f t="shared" si="4"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G83" s="94">
+        <f t="shared" si="5"/>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
       <c r="J83" s="13"/>
       <c r="K83" s="12"/>
       <c r="M83" s="3">
-        <f t="shared" ref="M83" si="32">D82/(7/12/3.281)</f>
-        <v>21.76709142857143</v>
+        <f t="shared" ref="M83" si="23">D82/(7/12/3.281)</f>
+        <v>15.861291428571427</v>
       </c>
       <c r="N83" s="3">
-        <f t="shared" si="23"/>
-        <v>21</v>
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="O83" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5103,34 +5249,34 @@
         <v>16</v>
       </c>
       <c r="D84" s="14">
-        <v>4.0599999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E84" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F84" s="12">
-        <f t="shared" si="21"/>
-        <v>25.663209876543206</v>
-      </c>
-      <c r="G84" s="14">
-        <f t="shared" si="22"/>
-        <v>2.5663209876543205E-2</v>
+      <c r="F84" s="94">
+        <f t="shared" si="4"/>
+        <v>25.916049382716047</v>
+      </c>
+      <c r="G84" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5916049382716046E-2</v>
       </c>
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
       <c r="J84" s="13"/>
       <c r="K84" s="12"/>
       <c r="M84" s="3">
-        <f t="shared" ref="M84" si="33">D85/(7/12/3.281)</f>
+        <f t="shared" ref="M84" si="24">D85/(7/12/3.281)</f>
         <v>16.479994285714287</v>
       </c>
       <c r="N84" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O84" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5138,37 +5284,37 @@
       <c r="A85" s="10"/>
       <c r="B85" s="16"/>
       <c r="C85" s="12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D85" s="14">
         <v>2.93</v>
       </c>
       <c r="E85" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F85" s="12">
-        <f t="shared" si="21"/>
-        <v>25.465679012345682</v>
-      </c>
-      <c r="G85" s="14">
-        <f t="shared" si="22"/>
-        <v>2.5465679012345682E-2</v>
+      <c r="F85" s="94">
+        <f t="shared" si="4"/>
+        <v>26.623209876543207</v>
+      </c>
+      <c r="G85" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6623209876543208E-2</v>
       </c>
       <c r="H85" s="12"/>
       <c r="I85" s="12"/>
       <c r="J85" s="13"/>
       <c r="K85" s="12"/>
       <c r="M85" s="3">
-        <f t="shared" ref="M85" si="34">D84/(7/12/3.281)</f>
-        <v>22.835759999999997</v>
+        <f t="shared" ref="M85" si="25">D84/(7/12/3.281)</f>
+        <v>23.060742857142856</v>
       </c>
       <c r="N85" s="3">
-        <f t="shared" si="23"/>
-        <v>22</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="O85" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5179,34 +5325,34 @@
         <v>16</v>
       </c>
       <c r="D86" s="14">
-        <v>4.0999999999999996</v>
+        <v>3.55</v>
       </c>
       <c r="E86" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F86" s="12">
-        <f t="shared" si="21"/>
-        <v>25.916049382716047</v>
-      </c>
-      <c r="G86" s="14">
-        <f t="shared" si="22"/>
-        <v>2.5916049382716046E-2</v>
+      <c r="F86" s="94">
+        <f t="shared" si="4"/>
+        <v>22.439506172839504</v>
+      </c>
+      <c r="G86" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2439506172839505E-2</v>
       </c>
       <c r="H86" s="12"/>
       <c r="I86" s="12"/>
       <c r="J86" s="13"/>
       <c r="K86" s="12"/>
       <c r="M86" s="3">
-        <f t="shared" ref="M86" si="35">D87/(7/12/3.281)</f>
+        <f t="shared" ref="M86" si="26">D87/(7/12/3.281)</f>
         <v>16.536239999999999</v>
       </c>
       <c r="N86" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O86" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5214,37 +5360,37 @@
       <c r="A87" s="10"/>
       <c r="B87" s="16"/>
       <c r="C87" s="12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D87" s="14">
         <v>2.94</v>
       </c>
       <c r="E87" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F87" s="12">
-        <f t="shared" si="21"/>
-        <v>26.714074074074073</v>
-      </c>
-      <c r="G87" s="14">
-        <f t="shared" si="22"/>
-        <v>2.6714074074074074E-2</v>
+      <c r="F87" s="94">
+        <f t="shared" si="4"/>
+        <v>22.068148148148147</v>
+      </c>
+      <c r="G87" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2068148148148146E-2</v>
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
       <c r="J87" s="13"/>
       <c r="K87" s="12"/>
       <c r="M87" s="3">
-        <f t="shared" ref="M87" si="36">D86/(7/12/3.281)</f>
-        <v>23.060742857142856</v>
+        <f t="shared" ref="M87" si="27">D86/(7/12/3.281)</f>
+        <v>19.967228571428571</v>
       </c>
       <c r="N87" s="3">
-        <f t="shared" si="23"/>
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="O87" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5252,37 +5398,37 @@
       <c r="A88" s="10"/>
       <c r="B88" s="16"/>
       <c r="C88" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" s="14">
-        <v>4.13</v>
+        <v>3.56</v>
       </c>
       <c r="E88" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F88" s="12">
-        <f t="shared" si="21"/>
-        <v>24.474074074074071</v>
-      </c>
-      <c r="G88" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4474074074074072E-2</v>
+      <c r="F88" s="94">
+        <f t="shared" si="4"/>
+        <v>22.502716049382716</v>
+      </c>
+      <c r="G88" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2502716049382716E-2</v>
       </c>
       <c r="H88" s="12"/>
       <c r="I88" s="12"/>
       <c r="J88" s="13"/>
       <c r="K88" s="12"/>
       <c r="M88" s="3">
-        <f t="shared" ref="M88" si="37">D89/(7/12/3.281)</f>
-        <v>15.186342857142858</v>
+        <f t="shared" ref="M88" si="28">D89/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
       </c>
       <c r="N88" s="3">
-        <f t="shared" si="23"/>
-        <v>15</v>
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="O88" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5290,37 +5436,37 @@
       <c r="A89" s="10"/>
       <c r="B89" s="16"/>
       <c r="C89" s="12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D89" s="14">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="E89" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F89" s="12">
-        <f t="shared" si="21"/>
-        <v>24.533333333333331</v>
-      </c>
-      <c r="G89" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4533333333333331E-2</v>
+      <c r="F89" s="94">
+        <f t="shared" si="4"/>
+        <v>23.229629629629628</v>
+      </c>
+      <c r="G89" s="94">
+        <f t="shared" si="5"/>
+        <v>2.3229629629629628E-2</v>
       </c>
       <c r="H89" s="12"/>
       <c r="I89" s="12"/>
       <c r="J89" s="13"/>
       <c r="K89" s="12"/>
       <c r="M89" s="3">
-        <f t="shared" ref="M89" si="38">D88/(7/12/3.281)</f>
-        <v>23.229479999999999</v>
+        <f t="shared" ref="M89" si="29">D88/(7/12/3.281)</f>
+        <v>20.023474285714286</v>
       </c>
       <c r="N89" s="3">
-        <f t="shared" si="23"/>
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="O89" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5331,34 +5477,34 @@
         <v>16</v>
       </c>
       <c r="D90" s="14">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="E90" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F90" s="12">
-        <f t="shared" si="21"/>
-        <v>17.825185185185184</v>
-      </c>
-      <c r="G90" s="14">
-        <f t="shared" si="22"/>
-        <v>1.7825185185185183E-2</v>
+      <c r="F90" s="94">
+        <f t="shared" si="4"/>
+        <v>40.45432098765432</v>
+      </c>
+      <c r="G90" s="94">
+        <f t="shared" si="5"/>
+        <v>4.0454320987654321E-2</v>
       </c>
       <c r="H90" s="12"/>
       <c r="I90" s="12"/>
       <c r="J90" s="13"/>
       <c r="K90" s="12"/>
       <c r="M90" s="3">
-        <f t="shared" ref="M90" si="39">D91/(7/12/3.281)</f>
-        <v>16.704977142857143</v>
+        <f t="shared" ref="M90" si="30">D91/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
       </c>
       <c r="N90" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O90" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5366,38 +5512,38 @@
       <c r="A91" s="10"/>
       <c r="B91" s="16"/>
       <c r="C91" s="12">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D91" s="14">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="E91" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F91" s="12">
-        <f t="shared" si="21"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="G91" s="14">
-        <f t="shared" si="22"/>
-        <v>1.7600000000000001E-2</v>
+      <c r="F91" s="94">
+        <f t="shared" si="4"/>
+        <v>34.725925925925928</v>
+      </c>
+      <c r="G91" s="94">
+        <f t="shared" si="5"/>
+        <v>3.4725925925925931E-2</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
       <c r="J91" s="13"/>
       <c r="K91" s="12"/>
       <c r="M91" s="3">
-        <f t="shared" ref="M91" si="40">D90/(7/12/3.281)</f>
-        <v>15.861291428571427</v>
+        <f t="shared" ref="M91" si="31">D90/(7/12/3.281)</f>
+        <v>35.997257142857144</v>
       </c>
       <c r="N91" s="3">
-        <f t="shared" si="23"/>
-        <v>15</v>
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="O91" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
@@ -5407,34 +5553,34 @@
         <v>16</v>
       </c>
       <c r="D92" s="14">
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="E92" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F92" s="12">
-        <f t="shared" si="21"/>
-        <v>25.916049382716047</v>
-      </c>
-      <c r="G92" s="14">
-        <f t="shared" si="22"/>
-        <v>2.5916049382716046E-2</v>
+      <c r="F92" s="94">
+        <f t="shared" si="4"/>
+        <v>24.019753086419751</v>
+      </c>
+      <c r="G92" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4019753086419751E-2</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
       <c r="J92" s="13"/>
       <c r="K92" s="12"/>
       <c r="M92" s="3">
-        <f t="shared" ref="M92" si="41">D93/(7/12/3.281)</f>
+        <f t="shared" ref="M92" si="32">D93/(7/12/3.281)</f>
         <v>16.479994285714287</v>
       </c>
       <c r="N92" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="O92" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5442,606 +5588,310 @@
       <c r="A93" s="10"/>
       <c r="B93" s="16"/>
       <c r="C93" s="12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D93" s="14">
         <v>2.93</v>
       </c>
       <c r="E93" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="F93" s="12">
-        <f t="shared" si="21"/>
-        <v>26.623209876543207</v>
-      </c>
-      <c r="G93" s="14">
-        <f t="shared" si="22"/>
-        <v>2.6623209876543208E-2</v>
+      <c r="F93" s="94">
+        <f t="shared" si="4"/>
+        <v>23.150617283950616</v>
+      </c>
+      <c r="G93" s="94">
+        <f t="shared" si="5"/>
+        <v>2.3150617283950615E-2</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
       <c r="J93" s="13"/>
       <c r="K93" s="12"/>
       <c r="M93" s="3">
-        <f t="shared" ref="M93" si="42">D92/(7/12/3.281)</f>
-        <v>23.060742857142856</v>
+        <f t="shared" ref="M93" si="33">D92/(7/12/3.281)</f>
+        <v>21.373371428571428</v>
       </c>
       <c r="N93" s="3">
-        <f t="shared" si="23"/>
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>21</v>
       </c>
       <c r="O93" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="10"/>
-      <c r="B94" s="16"/>
-      <c r="C94" s="12">
-        <v>16</v>
-      </c>
-      <c r="D94" s="14">
-        <v>3.55</v>
-      </c>
-      <c r="E94" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F94" s="12">
-        <f t="shared" si="21"/>
-        <v>22.439506172839504</v>
-      </c>
-      <c r="G94" s="14">
-        <f t="shared" si="22"/>
-        <v>2.2439506172839505E-2</v>
-      </c>
-      <c r="H94" s="12"/>
-      <c r="I94" s="12"/>
-      <c r="J94" s="13"/>
-      <c r="K94" s="12"/>
-      <c r="M94" s="3">
-        <f t="shared" ref="M94" si="43">D95/(7/12/3.281)</f>
-        <v>16.536239999999999</v>
-      </c>
-      <c r="N94" s="3">
-        <f t="shared" si="23"/>
-        <v>16</v>
-      </c>
-      <c r="O94" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="17"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="95">
+        <f>SUM(G66:G93)</f>
+        <v>0.71455209876543213</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="I94" s="2">
+        <v>124355</v>
+      </c>
+      <c r="J94" s="19">
+        <f>G94*I94</f>
+        <v>88858.126241975318</v>
+      </c>
+      <c r="K94" s="18"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="10"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="12">
-        <v>19</v>
-      </c>
-      <c r="D95" s="14">
-        <v>2.94</v>
-      </c>
-      <c r="E95" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F95" s="12">
-        <f t="shared" si="21"/>
-        <v>22.068148148148147</v>
-      </c>
-      <c r="G95" s="14">
-        <f t="shared" si="22"/>
-        <v>2.2068148148148146E-2</v>
-      </c>
+      <c r="B95" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
-      <c r="J95" s="13"/>
+      <c r="J95" s="13">
+        <f>0.13*G94*110000</f>
+        <v>10218.095012345681</v>
+      </c>
       <c r="K95" s="12"/>
-      <c r="M95" s="3">
-        <f t="shared" ref="M95" si="44">D94/(7/12/3.281)</f>
-        <v>19.967228571428571</v>
-      </c>
-      <c r="N95" s="3">
-        <f t="shared" si="23"/>
-        <v>19</v>
-      </c>
-      <c r="O95" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="10"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="12">
-        <v>16</v>
-      </c>
-      <c r="D96" s="14">
-        <v>3.56</v>
-      </c>
-      <c r="E96" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F96" s="12">
-        <f t="shared" si="21"/>
-        <v>22.502716049382716</v>
-      </c>
-      <c r="G96" s="14">
-        <f t="shared" si="22"/>
-        <v>2.2502716049382716E-2</v>
-      </c>
+      <c r="B96" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
-      <c r="J96" s="13"/>
+      <c r="J96" s="13">
+        <f>0.13*G94*960</f>
+        <v>89.176101925925934</v>
+      </c>
       <c r="K96" s="12"/>
-      <c r="M96" s="3">
-        <f t="shared" ref="M96" si="45">D97/(7/12/3.281)</f>
-        <v>16.536239999999999</v>
-      </c>
-      <c r="N96" s="3">
-        <f t="shared" si="23"/>
-        <v>16</v>
-      </c>
-      <c r="O96" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="10"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="12">
-        <v>20</v>
-      </c>
-      <c r="D97" s="14">
-        <v>2.94</v>
-      </c>
-      <c r="E97" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F97" s="12">
-        <f t="shared" si="21"/>
-        <v>23.229629629629628</v>
-      </c>
-      <c r="G97" s="14">
-        <f t="shared" si="22"/>
-        <v>2.3229629629629628E-2</v>
-      </c>
+      <c r="B97" s="22"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
       <c r="J97" s="13"/>
       <c r="K97" s="12"/>
-      <c r="M97" s="3">
-        <f t="shared" ref="M97" si="46">D96/(7/12/3.281)</f>
-        <v>20.023474285714286</v>
-      </c>
-      <c r="N97" s="3">
-        <f t="shared" si="23"/>
+    </row>
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="15">
+        <v>5</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98" s="17">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="20">
+        <f t="shared" ref="G98" si="34">PRODUCT(C98:F98)</f>
+        <v>1</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I98" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J98" s="20">
+        <f>G98*I98</f>
+        <v>5000</v>
+      </c>
+      <c r="K98" s="18"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="18"/>
+    </row>
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="15">
+        <v>6</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="17">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="20">
+        <f t="shared" ref="G100" si="35">PRODUCT(C100:F100)</f>
+        <v>1</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="2">
+        <v>500</v>
+      </c>
+      <c r="J100" s="20">
+        <f>G100*I100</f>
+        <v>500</v>
+      </c>
+      <c r="K100" s="18"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="18"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="26"/>
+      <c r="B102" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="28"/>
+      <c r="D102" s="29"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13">
+        <f>SUM(J9:J100)</f>
+        <v>565780.32579845074</v>
+      </c>
+      <c r="K102" s="30"/>
+    </row>
+    <row r="104" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="31"/>
+      <c r="B104" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="74">
+        <f>J102</f>
+        <v>565780.32579845074</v>
+      </c>
+      <c r="D104" s="75"/>
+      <c r="E104" s="33">
+        <v>100</v>
+      </c>
+      <c r="F104" s="31"/>
+      <c r="G104" s="34"/>
+      <c r="H104" s="31"/>
+      <c r="I104" s="35"/>
+      <c r="J104" s="36"/>
+      <c r="K104" s="37"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B105" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="O97" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="10"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="12">
-        <v>16</v>
-      </c>
-      <c r="D98" s="14">
-        <v>6.4</v>
-      </c>
-      <c r="E98" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F98" s="12">
-        <f t="shared" si="21"/>
-        <v>40.45432098765432</v>
-      </c>
-      <c r="G98" s="14">
-        <f t="shared" si="22"/>
-        <v>4.0454320987654321E-2</v>
-      </c>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="13"/>
-      <c r="K98" s="12"/>
-      <c r="M98" s="3">
-        <f t="shared" ref="M98" si="47">D99/(7/12/3.281)</f>
-        <v>16.479994285714287</v>
-      </c>
-      <c r="N98" s="3">
-        <f t="shared" si="23"/>
-        <v>16</v>
-      </c>
-      <c r="O98" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="10"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="12">
-        <v>35</v>
-      </c>
-      <c r="D99" s="14">
-        <v>2.93</v>
-      </c>
-      <c r="E99" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F99" s="12">
-        <f t="shared" si="21"/>
-        <v>40.513580246913584</v>
-      </c>
-      <c r="G99" s="14">
-        <f t="shared" si="22"/>
-        <v>4.0513580246913587E-2</v>
-      </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="12"/>
-      <c r="M99" s="3">
-        <f t="shared" ref="M99" si="48">D98/(7/12/3.281)</f>
-        <v>35.997257142857144</v>
-      </c>
-      <c r="N99" s="3">
-        <f t="shared" si="23"/>
-        <v>35</v>
-      </c>
-      <c r="O99" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="12">
-        <v>16</v>
-      </c>
-      <c r="D100" s="14">
-        <v>3.8</v>
-      </c>
-      <c r="E100" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F100" s="12">
-        <f t="shared" si="21"/>
-        <v>24.019753086419751</v>
-      </c>
-      <c r="G100" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4019753086419751E-2</v>
-      </c>
-      <c r="H100" s="12"/>
-      <c r="I100" s="12"/>
-      <c r="J100" s="13"/>
-      <c r="K100" s="12"/>
-      <c r="M100" s="3">
-        <f t="shared" ref="M100" si="49">D101/(7/12/3.281)</f>
-        <v>16.479994285714287</v>
-      </c>
-      <c r="N100" s="3">
-        <f t="shared" si="23"/>
-        <v>16</v>
-      </c>
-      <c r="O100" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="10"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="12">
+      <c r="C105" s="78">
+        <v>500000</v>
+      </c>
+      <c r="D105" s="79"/>
+      <c r="E105" s="33"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B106" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="14">
-        <v>2.93</v>
-      </c>
-      <c r="E101" s="14">
-        <f t="shared" si="20"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F101" s="12">
-        <f t="shared" si="21"/>
-        <v>24.308148148148149</v>
-      </c>
-      <c r="G101" s="14">
-        <f t="shared" si="22"/>
-        <v>2.4308148148148148E-2</v>
-      </c>
-      <c r="H101" s="12"/>
-      <c r="I101" s="12"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="12"/>
-      <c r="M101" s="3">
-        <f t="shared" ref="M101" si="50">D100/(7/12/3.281)</f>
-        <v>21.373371428571428</v>
-      </c>
-      <c r="N101" s="3">
-        <f t="shared" si="23"/>
-        <v>21</v>
-      </c>
-      <c r="O101" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="15"/>
-      <c r="B102" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C102" s="17"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="19">
-        <f>SUM(G74:G101)</f>
-        <v>0.7214972839506173</v>
-      </c>
-      <c r="H102" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I102" s="2">
-        <v>124355</v>
-      </c>
-      <c r="J102" s="19">
-        <f>G102*I102</f>
-        <v>89721.794745679013</v>
-      </c>
-      <c r="K102" s="18"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="10"/>
-      <c r="B103" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="12"/>
-      <c r="I103" s="12"/>
-      <c r="J103" s="13">
-        <f>0.13*G102*110000</f>
-        <v>10317.411160493828</v>
-      </c>
-      <c r="K103" s="12"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="10"/>
-      <c r="B104" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="12"/>
-      <c r="I104" s="12"/>
-      <c r="J104" s="13">
-        <f>0.13*G102*960</f>
-        <v>90.042861037037042</v>
-      </c>
-      <c r="K104" s="12"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="10"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="12"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="12"/>
-      <c r="I105" s="12"/>
-      <c r="J105" s="13"/>
-      <c r="K105" s="12"/>
-    </row>
-    <row r="106" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="15">
-        <v>5</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C106" s="17">
-        <v>1</v>
-      </c>
-      <c r="D106" s="1"/>
-      <c r="E106" s="18"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="20">
-        <f t="shared" ref="G106" si="51">PRODUCT(C106:F106)</f>
-        <v>1</v>
-      </c>
-      <c r="H106" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I106" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J106" s="20">
-        <f>G106*I106</f>
-        <v>5000</v>
-      </c>
-      <c r="K106" s="18"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="17"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="13"/>
-      <c r="K107" s="18"/>
-    </row>
-    <row r="108" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="15">
-        <v>6</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" s="17">
-        <v>1</v>
-      </c>
-      <c r="D108" s="1"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="20">
-        <f t="shared" ref="G108" si="52">PRODUCT(C108:F108)</f>
-        <v>1</v>
-      </c>
-      <c r="H108" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I108" s="2">
-        <v>500</v>
-      </c>
-      <c r="J108" s="20">
-        <f>G108*I108</f>
-        <v>500</v>
-      </c>
-      <c r="K108" s="18"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="13"/>
-      <c r="K109" s="18"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="26"/>
-      <c r="B110" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C110" s="28"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
-      <c r="F110" s="29"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
-      <c r="J110" s="13">
-        <f>SUM(J9:J108)</f>
-        <v>568312.91840178403</v>
-      </c>
-      <c r="K110" s="30"/>
-    </row>
-    <row r="112" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="31"/>
-      <c r="B112" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C112" s="66">
-        <f>J110</f>
-        <v>568312.91840178403</v>
-      </c>
-      <c r="D112" s="67"/>
-      <c r="E112" s="33">
-        <v>100</v>
-      </c>
-      <c r="F112" s="31"/>
-      <c r="G112" s="34"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
-      <c r="K112" s="37"/>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B113" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C113" s="70">
-        <v>500000</v>
-      </c>
-      <c r="D113" s="71"/>
-      <c r="E113" s="33"/>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B114" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" s="70">
-        <f>C113-C116-C117</f>
+      <c r="C106" s="78">
+        <f>C105-C108-C109</f>
         <v>475000</v>
       </c>
-      <c r="D114" s="71"/>
-      <c r="E114" s="33">
-        <f>C114/C112*100</f>
-        <v>83.580714887812206</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B115" s="32" t="s">
+      <c r="D106" s="79"/>
+      <c r="E106" s="33">
+        <f>C106/C104*100</f>
+        <v>83.95484578394661</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B107" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C115" s="72">
-        <f>C112-C114</f>
-        <v>93312.918401784031</v>
-      </c>
-      <c r="D115" s="72"/>
-      <c r="E115" s="33">
-        <f>100-E114</f>
-        <v>16.419285112187794</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B116" s="32" t="s">
+      <c r="C107" s="80">
+        <f>C104-C106</f>
+        <v>90780.325798450736</v>
+      </c>
+      <c r="D107" s="80"/>
+      <c r="E107" s="33">
+        <f>100-E106</f>
+        <v>16.04515421605339</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B108" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C116" s="66">
-        <f>C113*0.03</f>
+      <c r="C108" s="74">
+        <f>C105*0.03</f>
         <v>15000</v>
       </c>
-      <c r="D116" s="67"/>
-      <c r="E116" s="33">
+      <c r="D108" s="75"/>
+      <c r="E108" s="33">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B117" s="32" t="s">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B109" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C117" s="66">
-        <f>C113*0.02</f>
+      <c r="C109" s="74">
+        <f>C105*0.02</f>
         <v>10000</v>
       </c>
-      <c r="D117" s="67"/>
-      <c r="E117" s="33">
+      <c r="D109" s="75"/>
+      <c r="E109" s="33">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C107:D107"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -6049,23 +5899,12 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="107" max="10" man="1"/>
-  </rowBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6578,4 +6417,2937 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AFF1DF-EC35-4661-8E97-AEC65E65FFCD}">
+  <dimension ref="A1:P109"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="3"/>
+    <col min="8" max="8" width="5" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="73" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="4"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="5"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="66" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="21" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>1</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14">
+        <f>'chainage measurement'!C3</f>
+        <v>5</v>
+      </c>
+      <c r="E10" s="14">
+        <f>'chainage measurement'!E3</f>
+        <v>3.3907345321548306</v>
+      </c>
+      <c r="F10" s="14">
+        <f>'chainage measurement'!G3-0.15</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G10" s="14">
+        <f t="shared" ref="G10:G23" si="0">PRODUCT(C10:F10)</f>
+        <v>2.1530113609639026</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14">
+        <f>'chainage measurement'!C4</f>
+        <v>5</v>
+      </c>
+      <c r="E11" s="14">
+        <f>'chainage measurement'!E4</f>
+        <v>3.3145382505333738</v>
+      </c>
+      <c r="F11" s="14">
+        <f>'chainage measurement'!G4-0.15</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G11" s="14">
+        <f t="shared" si="0"/>
+        <v>2.1046290831894328</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
+        <f>'chainage measurement'!C5</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="14">
+        <f>'chainage measurement'!E5</f>
+        <v>3.0219445291069795</v>
+      </c>
+      <c r="F12" s="14">
+        <f>'chainage measurement'!G5-0.15</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G12" s="14">
+        <f t="shared" si="0"/>
+        <v>1.571223876240704</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14">
+        <f>'chainage measurement'!C6</f>
+        <v>5</v>
+      </c>
+      <c r="E13" s="14">
+        <f>'chainage measurement'!E6</f>
+        <v>2.9838463882962509</v>
+      </c>
+      <c r="F13" s="14">
+        <f>'chainage measurement'!G6-0.15</f>
+        <v>0.11033729553997765</v>
+      </c>
+      <c r="G13" s="14">
+        <f t="shared" si="0"/>
+        <v>1.6461477039566916</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <f>'chainage measurement'!C7</f>
+        <v>5</v>
+      </c>
+      <c r="E14" s="14">
+        <f>'chainage measurement'!E7</f>
+        <v>3.1621456872904599</v>
+      </c>
+      <c r="F14" s="14">
+        <f>'chainage measurement'!G7-0.15</f>
+        <v>0.11668698567509903</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="0"/>
+        <v>1.8449062425771903</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <f>'chainage measurement'!C8</f>
+        <v>5</v>
+      </c>
+      <c r="E15" s="14">
+        <f>'chainage measurement'!E8</f>
+        <v>3.0859494056690031</v>
+      </c>
+      <c r="F15" s="14">
+        <f>'chainage measurement'!G8-0.15</f>
+        <v>0.11668698567509903</v>
+      </c>
+      <c r="G15" s="14">
+        <f t="shared" si="0"/>
+        <v>1.8004506704668966</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <f>'chainage measurement'!C9</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="14">
+        <f>'chainage measurement'!E9</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F16" s="14">
+        <f>'chainage measurement'!G9-0.15</f>
+        <v>0.11033729553997765</v>
+      </c>
+      <c r="G16" s="14">
+        <f t="shared" si="0"/>
+        <v>1.7304728391491617</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="12">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
+        <f>'chainage measurement'!C10</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="14">
+        <f>'chainage measurement'!E10</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F17" s="14">
+        <f>'chainage measurement'!G10-0.15</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G17" s="14">
+        <f t="shared" si="0"/>
+        <v>1.6308875968059711</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <f>'chainage measurement'!C11</f>
+        <v>5</v>
+      </c>
+      <c r="E18" s="14">
+        <f>'chainage measurement'!E11</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F18" s="14">
+        <f>'chainage measurement'!G11-0.15</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" si="0"/>
+        <v>1.6243111176467186</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14">
+        <f>'chainage measurement'!C12</f>
+        <v>5</v>
+      </c>
+      <c r="E19" s="14">
+        <f>'chainage measurement'!E12</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F19" s="14">
+        <f>'chainage measurement'!G12-0.15</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G19" s="14">
+        <f t="shared" si="0"/>
+        <v>1.6639284619795653</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <f>'chainage measurement'!C13</f>
+        <v>5</v>
+      </c>
+      <c r="E20" s="14">
+        <f>'chainage measurement'!E13</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F20" s="14">
+        <f>'chainage measurement'!G13-0.15</f>
+        <v>7.8588844864370622E-2</v>
+      </c>
+      <c r="G20" s="14">
+        <f t="shared" si="0"/>
+        <v>1.2275764398960665</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14">
+        <f>'chainage measurement'!C14</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E21" s="14">
+        <f>'chainage measurement'!E14</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F21" s="14">
+        <f>'chainage measurement'!G14-0.15</f>
+        <v>6.5889464594127783E-2</v>
+      </c>
+      <c r="G21" s="14">
+        <f t="shared" si="0"/>
+        <v>0.64267708748628227</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <f>'chainage measurement'!C15</f>
+        <v>5</v>
+      </c>
+      <c r="E22" s="14">
+        <f>'chainage measurement'!E15</f>
+        <v>3.5557756781469063</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="G22" s="14">
+        <f t="shared" si="0"/>
+        <v>2.6668317586101797</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <f>'chainage measurement'!C16</f>
+        <v>0.35558264756679875</v>
+      </c>
+      <c r="E23" s="14">
+        <f>'chainage measurement'!E16</f>
+        <v>3.8351112465711674</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="14">
+        <f t="shared" si="0"/>
+        <v>0.20455485161534726</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19">
+        <f>SUM(G10:G23)</f>
+        <v>22.511609090584113</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="2">
+        <v>62.95</v>
+      </c>
+      <c r="J24" s="19">
+        <f>G24*I24</f>
+        <v>1417.10579225227</v>
+      </c>
+      <c r="K24" s="18"/>
+    </row>
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13">
+        <f>0.13*G24*18612/360</f>
+        <v>151.3005246978158</v>
+      </c>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>2</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="16" t="str">
+        <f>B10</f>
+        <v>-for road</v>
+      </c>
+      <c r="C28" s="12">
+        <f>C10</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <f>D10</f>
+        <v>5</v>
+      </c>
+      <c r="E28" s="14">
+        <f>E10</f>
+        <v>3.3907345321548306</v>
+      </c>
+      <c r="F28" s="14">
+        <f>F10</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G28" s="14">
+        <f t="shared" ref="G28:G39" si="1">PRODUCT(C28:F28)</f>
+        <v>2.1530113609639026</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="12">
+        <f>C11</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <f>D11</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="14">
+        <f>E11</f>
+        <v>3.3145382505333738</v>
+      </c>
+      <c r="F29" s="14">
+        <f>F11</f>
+        <v>0.12699380270242813</v>
+      </c>
+      <c r="G29" s="14">
+        <f t="shared" si="1"/>
+        <v>2.1046290831894328</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="12">
+        <f>C12</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <f>D12</f>
+        <v>5</v>
+      </c>
+      <c r="E30" s="14">
+        <f>E12</f>
+        <v>3.0219445291069795</v>
+      </c>
+      <c r="F30" s="14">
+        <f>F12</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G30" s="14">
+        <f t="shared" si="1"/>
+        <v>1.571223876240704</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="12">
+        <f>C13</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <f>D13</f>
+        <v>5</v>
+      </c>
+      <c r="E31" s="14">
+        <f>E13</f>
+        <v>2.9838463882962509</v>
+      </c>
+      <c r="F31" s="14">
+        <f>F13</f>
+        <v>0.11033729553997765</v>
+      </c>
+      <c r="G31" s="14">
+        <f t="shared" si="1"/>
+        <v>1.6461477039566916</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="12">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="14">
+        <f>D14</f>
+        <v>5</v>
+      </c>
+      <c r="E32" s="14">
+        <f>E14</f>
+        <v>3.1621456872904599</v>
+      </c>
+      <c r="F32" s="14">
+        <f>F14</f>
+        <v>0.11668698567509903</v>
+      </c>
+      <c r="G32" s="14">
+        <f t="shared" si="1"/>
+        <v>1.8449062425771903</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="12">
+        <f>C15</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <f>D15</f>
+        <v>5</v>
+      </c>
+      <c r="E33" s="14">
+        <f>E15</f>
+        <v>3.0859494056690031</v>
+      </c>
+      <c r="F33" s="14">
+        <f>F15</f>
+        <v>0.11668698567509903</v>
+      </c>
+      <c r="G33" s="14">
+        <f t="shared" si="1"/>
+        <v>1.8004506704668966</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="10"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="12">
+        <f>C16</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="14">
+        <f>D16</f>
+        <v>5</v>
+      </c>
+      <c r="E34" s="14">
+        <f>E16</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F34" s="14">
+        <f>F16</f>
+        <v>0.11033729553997765</v>
+      </c>
+      <c r="G34" s="14">
+        <f t="shared" si="1"/>
+        <v>1.7304728391491617</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="12">
+        <f>C17</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="14">
+        <f>D17</f>
+        <v>5</v>
+      </c>
+      <c r="E35" s="14">
+        <f>E17</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F35" s="14">
+        <f>F17</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G35" s="14">
+        <f t="shared" si="1"/>
+        <v>1.6308875968059711</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="12">
+        <f>C18</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="14">
+        <f>D18</f>
+        <v>5</v>
+      </c>
+      <c r="E36" s="14">
+        <f>E18</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F36" s="14">
+        <f>F18</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G36" s="14">
+        <f t="shared" si="1"/>
+        <v>1.6243111176467186</v>
+      </c>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="12">
+        <f>C19</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="14">
+        <f>D19</f>
+        <v>5</v>
+      </c>
+      <c r="E37" s="14">
+        <f>E19</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F37" s="14">
+        <f>F19</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G37" s="14">
+        <f t="shared" si="1"/>
+        <v>1.6639284619795653</v>
+      </c>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="12">
+        <f>C20</f>
+        <v>1</v>
+      </c>
+      <c r="D38" s="14">
+        <f>D20</f>
+        <v>5</v>
+      </c>
+      <c r="E38" s="14">
+        <f>E20</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F38" s="14">
+        <f>F20</f>
+        <v>7.8588844864370622E-2</v>
+      </c>
+      <c r="G38" s="14">
+        <f t="shared" si="1"/>
+        <v>1.2275764398960665</v>
+      </c>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="12">
+        <f>C21</f>
+        <v>1</v>
+      </c>
+      <c r="D39" s="14">
+        <f>D21</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E39" s="14">
+        <f>E21</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F39" s="14">
+        <f>F21</f>
+        <v>6.5889464594127783E-2</v>
+      </c>
+      <c r="G39" s="14">
+        <f t="shared" si="1"/>
+        <v>0.64267708748628227</v>
+      </c>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19">
+        <f>SUM(G28:G39)</f>
+        <v>19.640222480358585</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="2">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J40" s="19">
+        <f>G40*I40</f>
+        <v>87566.324733128364</v>
+      </c>
+      <c r="K40" s="18"/>
+    </row>
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13">
+        <f>0.13*G40*14817.6/5</f>
+        <v>7566.544976248997</v>
+      </c>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>3</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="10"/>
+      <c r="B44" s="16" t="str">
+        <f>B28</f>
+        <v>-for road</v>
+      </c>
+      <c r="C44" s="12">
+        <f>C10</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="14">
+        <f>D10</f>
+        <v>5</v>
+      </c>
+      <c r="E44" s="14">
+        <f>E10</f>
+        <v>3.3907345321548306</v>
+      </c>
+      <c r="F44" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G44" s="14">
+        <f t="shared" ref="G44:G57" si="2">PRODUCT(C44:F44)</f>
+        <v>2.5430508991161229</v>
+      </c>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="10"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="12">
+        <f>C11</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="14">
+        <f>D11</f>
+        <v>5</v>
+      </c>
+      <c r="E45" s="14">
+        <f>E11</f>
+        <v>3.3145382505333738</v>
+      </c>
+      <c r="F45" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G45" s="14">
+        <f t="shared" si="2"/>
+        <v>2.4859036879000302</v>
+      </c>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="10"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="12">
+        <f>C12</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="14">
+        <f>D12</f>
+        <v>5</v>
+      </c>
+      <c r="E46" s="14">
+        <f>E12</f>
+        <v>3.0219445291069795</v>
+      </c>
+      <c r="F46" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G46" s="14">
+        <f t="shared" si="2"/>
+        <v>2.2664583968302345</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="12">
+        <f>C13</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="14">
+        <f>D13</f>
+        <v>5</v>
+      </c>
+      <c r="E47" s="14">
+        <f>E13</f>
+        <v>2.9838463882962509</v>
+      </c>
+      <c r="F47" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G47" s="14">
+        <f t="shared" si="2"/>
+        <v>2.237884791222188</v>
+      </c>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="10"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="12">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D48" s="14">
+        <f>D14</f>
+        <v>5</v>
+      </c>
+      <c r="E48" s="14">
+        <f>E14</f>
+        <v>3.1621456872904599</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0.125</v>
+      </c>
+      <c r="G48" s="14">
+        <f t="shared" si="2"/>
+        <v>1.9763410545565374</v>
+      </c>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="10"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="12">
+        <f>C15</f>
+        <v>1</v>
+      </c>
+      <c r="D49" s="14">
+        <f>D15</f>
+        <v>5</v>
+      </c>
+      <c r="E49" s="14">
+        <f>E15</f>
+        <v>3.0859494056690031</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G49" s="14">
+        <f t="shared" si="2"/>
+        <v>2.3144620542517522</v>
+      </c>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="12"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="10"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="12">
+        <f>C16</f>
+        <v>1</v>
+      </c>
+      <c r="D50" s="14">
+        <f>D16</f>
+        <v>5</v>
+      </c>
+      <c r="E50" s="14">
+        <f>E16</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G50" s="14">
+        <f t="shared" si="2"/>
+        <v>2.3525220969216698</v>
+      </c>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="10"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="12">
+        <f>C17</f>
+        <v>1</v>
+      </c>
+      <c r="D51" s="14">
+        <f>D17</f>
+        <v>5</v>
+      </c>
+      <c r="E51" s="14">
+        <f>E17</f>
+        <v>3.1366961292288935</v>
+      </c>
+      <c r="F51" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="G51" s="14">
+        <f t="shared" si="2"/>
+        <v>2.3525220969216698</v>
+      </c>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="10"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="12">
+        <f>C18</f>
+        <v>1</v>
+      </c>
+      <c r="D52" s="14">
+        <f>D18</f>
+        <v>5</v>
+      </c>
+      <c r="E52" s="14">
+        <f>E18</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0.125</v>
+      </c>
+      <c r="G52" s="14">
+        <f t="shared" si="2"/>
+        <v>1.9525297165498323</v>
+      </c>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="12"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="10"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="12">
+        <f>C19</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="14">
+        <f>D19</f>
+        <v>5</v>
+      </c>
+      <c r="E53" s="14">
+        <f>E19</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F53" s="14">
+        <f>F37</f>
+        <v>0.10398760540485627</v>
+      </c>
+      <c r="G53" s="14">
+        <f t="shared" si="2"/>
+        <v>1.6639284619795653</v>
+      </c>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="10"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="12">
+        <f>C20</f>
+        <v>1</v>
+      </c>
+      <c r="D54" s="14">
+        <f>D20</f>
+        <v>5</v>
+      </c>
+      <c r="E54" s="14">
+        <f>E20</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="G54" s="14">
+        <f t="shared" si="2"/>
+        <v>1.5620237732398659</v>
+      </c>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="10"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="12">
+        <f>C21</f>
+        <v>1</v>
+      </c>
+      <c r="D55" s="14">
+        <f>D21</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E55" s="14">
+        <f>E21</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="G55" s="14">
+        <f t="shared" si="2"/>
+        <v>0.97538671993330961</v>
+      </c>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="10"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="12">
+        <f>C22</f>
+        <v>1</v>
+      </c>
+      <c r="D56" s="14">
+        <f>D22</f>
+        <v>5</v>
+      </c>
+      <c r="E56" s="14">
+        <f>E22</f>
+        <v>3.5557756781469063</v>
+      </c>
+      <c r="F56" s="14">
+        <f>F22</f>
+        <v>0.15</v>
+      </c>
+      <c r="G56" s="14">
+        <f t="shared" si="2"/>
+        <v>2.6668317586101797</v>
+      </c>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="10"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="12">
+        <f>C23</f>
+        <v>1</v>
+      </c>
+      <c r="D57" s="14">
+        <f>D23</f>
+        <v>0.35558264756679875</v>
+      </c>
+      <c r="E57" s="14">
+        <f>E23</f>
+        <v>3.8351112465711674</v>
+      </c>
+      <c r="F57" s="14">
+        <f>F23</f>
+        <v>0.15</v>
+      </c>
+      <c r="G57" s="14">
+        <f t="shared" si="2"/>
+        <v>0.20455485161534726</v>
+      </c>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="12"/>
+    </row>
+    <row r="58" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="17"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="19">
+        <f>SUM(G44:G57)</f>
+        <v>27.554400359648305</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="2">
+        <v>12000.5</v>
+      </c>
+      <c r="J58" s="19">
+        <f>G58*I58</f>
+        <v>330666.58151595946</v>
+      </c>
+      <c r="K58" s="18"/>
+    </row>
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="10"/>
+      <c r="B59" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="13">
+        <f>0.13*G58*67891.51/15</f>
+        <v>16212.818678862574</v>
+      </c>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10"/>
+      <c r="B60" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="13">
+        <f>0.13*G58*21432.6/15</f>
+        <v>5118.2078232843842</v>
+      </c>
+      <c r="K60" s="12"/>
+    </row>
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="10"/>
+      <c r="B61" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="13">
+        <f>0.13*G58*(27147.96+17146.08)/15</f>
+        <v>10577.629501454396</v>
+      </c>
+      <c r="K61" s="12"/>
+    </row>
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="10"/>
+      <c r="B62" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="13">
+        <f>0.13*G58*775/15</f>
+        <v>185.07372241563777</v>
+      </c>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10"/>
+      <c r="B63" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="13">
+        <f>0.13*G58*6923.4/15</f>
+        <v>1653.3411738999052</v>
+      </c>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="10"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" spans="1:16" s="21" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>4</v>
+      </c>
+      <c r="B65" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="32"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="10"/>
+      <c r="B66" s="16" t="str">
+        <f>B10</f>
+        <v>-for road</v>
+      </c>
+      <c r="C66" s="12">
+        <v>16</v>
+      </c>
+      <c r="D66" s="14">
+        <v>4</v>
+      </c>
+      <c r="E66" s="14">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F66" s="94">
+        <f>PRODUCT(C66:E66)</f>
+        <v>25.283950617283949</v>
+      </c>
+      <c r="G66" s="94">
+        <f>F66/1000</f>
+        <v>2.5283950617283949E-2</v>
+      </c>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="12"/>
+      <c r="M66" s="3">
+        <f>D67/(7/12/3.281)</f>
+        <v>16.311257142857141</v>
+      </c>
+      <c r="N66" s="3">
+        <f>TRUNC(M66,0)</f>
+        <v>16</v>
+      </c>
+      <c r="O66" s="3">
+        <f>C66-N66</f>
+        <v>0</v>
+      </c>
+      <c r="P66" s="47"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="10"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="12">
+        <v>22</v>
+      </c>
+      <c r="D67" s="14">
+        <v>2.9</v>
+      </c>
+      <c r="E67" s="14">
+        <f t="shared" ref="E67:E93" si="3">8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F67" s="94">
+        <f t="shared" ref="F67:F93" si="4">PRODUCT(C67:E67)</f>
+        <v>25.204938271604934</v>
+      </c>
+      <c r="G67" s="94">
+        <f t="shared" ref="G67:G93" si="5">F67/1000</f>
+        <v>2.5204938271604936E-2</v>
+      </c>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="12"/>
+      <c r="M67" s="3">
+        <f>D66/(7/12/3.281)</f>
+        <v>22.498285714285714</v>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" ref="N67:N93" si="6">TRUNC(M67,0)</f>
+        <v>22</v>
+      </c>
+      <c r="O67" s="3">
+        <f t="shared" ref="O67:O93" si="7">C67-N67</f>
+        <v>0</v>
+      </c>
+      <c r="P67" s="47"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="10"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="12">
+        <v>16</v>
+      </c>
+      <c r="D68" s="14">
+        <v>4.12</v>
+      </c>
+      <c r="E68" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F68" s="94">
+        <f t="shared" si="4"/>
+        <v>26.042469135802467</v>
+      </c>
+      <c r="G68" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6042469135802465E-2</v>
+      </c>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="12"/>
+      <c r="M68" s="3">
+        <f t="shared" ref="M68" si="8">D69/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O68" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="10"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="12">
+        <v>23</v>
+      </c>
+      <c r="D69" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E69" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F69" s="94">
+        <f t="shared" si="4"/>
+        <v>26.714074074074073</v>
+      </c>
+      <c r="G69" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6714074074074074E-2</v>
+      </c>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="12"/>
+      <c r="M69" s="3">
+        <f t="shared" ref="M69" si="9">D68/(7/12/3.281)</f>
+        <v>23.173234285714287</v>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O69" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="10"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="12">
+        <v>16</v>
+      </c>
+      <c r="D70" s="14">
+        <v>3.9</v>
+      </c>
+      <c r="E70" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F70" s="94">
+        <f t="shared" si="4"/>
+        <v>24.651851851851848</v>
+      </c>
+      <c r="G70" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4651851851851848E-2</v>
+      </c>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="12"/>
+      <c r="M70" s="3">
+        <f t="shared" ref="M70" si="10">D71/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N70" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O70" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="10"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="12">
+        <v>21</v>
+      </c>
+      <c r="D71" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E71" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F71" s="94">
+        <f t="shared" si="4"/>
+        <v>24.391111111111112</v>
+      </c>
+      <c r="G71" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4391111111111113E-2</v>
+      </c>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="12"/>
+      <c r="M71" s="3">
+        <f t="shared" ref="M71" si="11">D70/(7/12/3.281)</f>
+        <v>21.935828571428569</v>
+      </c>
+      <c r="N71" s="3">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="O71" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="10"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="12">
+        <v>15</v>
+      </c>
+      <c r="D72" s="14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E72" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F72" s="94">
+        <f t="shared" si="4"/>
+        <v>30.222222222222221</v>
+      </c>
+      <c r="G72" s="94">
+        <f t="shared" si="5"/>
+        <v>3.022222222222222E-2</v>
+      </c>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="12"/>
+      <c r="M72" s="3">
+        <f t="shared" ref="M72" si="12">D73/(7/12/3.281)</f>
+        <v>15.186342857142858</v>
+      </c>
+      <c r="N72" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="O72" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="10"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="12">
+        <v>28</v>
+      </c>
+      <c r="D73" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="E73" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F73" s="94">
+        <f t="shared" si="4"/>
+        <v>29.866666666666667</v>
+      </c>
+      <c r="G73" s="94">
+        <f t="shared" si="5"/>
+        <v>2.9866666666666666E-2</v>
+      </c>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="12"/>
+      <c r="M73" s="3">
+        <f t="shared" ref="M73" si="13">D72/(7/12/3.281)</f>
+        <v>28.685314285714284</v>
+      </c>
+      <c r="N73" s="3">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="O73" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="10"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="12">
+        <v>16</v>
+      </c>
+      <c r="D74" s="14">
+        <v>3.87</v>
+      </c>
+      <c r="E74" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F74" s="94">
+        <f t="shared" si="4"/>
+        <v>24.46222222222222</v>
+      </c>
+      <c r="G74" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4462222222222219E-2</v>
+      </c>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="12"/>
+      <c r="M74" s="3">
+        <f t="shared" ref="M74" si="14">D75/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N74" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O74" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="10"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="12">
+        <v>21</v>
+      </c>
+      <c r="D75" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E75" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F75" s="94">
+        <f t="shared" si="4"/>
+        <v>24.391111111111112</v>
+      </c>
+      <c r="G75" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4391111111111113E-2</v>
+      </c>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="12"/>
+      <c r="M75" s="3">
+        <f t="shared" ref="M75" si="15">D74/(7/12/3.281)</f>
+        <v>21.76709142857143</v>
+      </c>
+      <c r="N75" s="3">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="O75" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="10"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="12">
+        <v>16</v>
+      </c>
+      <c r="D76" s="14">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="E76" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F76" s="94">
+        <f t="shared" si="4"/>
+        <v>25.663209876543206</v>
+      </c>
+      <c r="G76" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5663209876543205E-2</v>
+      </c>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="12"/>
+      <c r="M76" s="3">
+        <f t="shared" ref="M76" si="16">D77/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
+      </c>
+      <c r="N76" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O76" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="10"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="12">
+        <v>22</v>
+      </c>
+      <c r="D77" s="14">
+        <v>2.93</v>
+      </c>
+      <c r="E77" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F77" s="94">
+        <f t="shared" si="4"/>
+        <v>25.465679012345682</v>
+      </c>
+      <c r="G77" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5465679012345682E-2</v>
+      </c>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="12"/>
+      <c r="M77" s="3">
+        <f t="shared" ref="M77" si="17">D76/(7/12/3.281)</f>
+        <v>22.835759999999997</v>
+      </c>
+      <c r="N77" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="O77" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="10"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="12">
+        <v>16</v>
+      </c>
+      <c r="D78" s="14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E78" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F78" s="94">
+        <f t="shared" si="4"/>
+        <v>25.916049382716047</v>
+      </c>
+      <c r="G78" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5916049382716046E-2</v>
+      </c>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="12"/>
+      <c r="M78" s="3">
+        <f t="shared" ref="M78" si="18">D79/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N78" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O78" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="10"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="12">
+        <v>23</v>
+      </c>
+      <c r="D79" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E79" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F79" s="94">
+        <f t="shared" si="4"/>
+        <v>26.714074074074073</v>
+      </c>
+      <c r="G79" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6714074074074074E-2</v>
+      </c>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="12"/>
+      <c r="M79" s="3">
+        <f t="shared" ref="M79" si="19">D78/(7/12/3.281)</f>
+        <v>23.060742857142856</v>
+      </c>
+      <c r="N79" s="3">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O79" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="10"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="12">
+        <v>15</v>
+      </c>
+      <c r="D80" s="14">
+        <v>4.13</v>
+      </c>
+      <c r="E80" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F80" s="94">
+        <f t="shared" si="4"/>
+        <v>24.474074074074071</v>
+      </c>
+      <c r="G80" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4474074074074072E-2</v>
+      </c>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="12"/>
+      <c r="M80" s="3">
+        <f t="shared" ref="M80" si="20">D81/(7/12/3.281)</f>
+        <v>15.186342857142858</v>
+      </c>
+      <c r="N80" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="O80" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="10"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="12">
+        <v>23</v>
+      </c>
+      <c r="D81" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="E81" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F81" s="94">
+        <f t="shared" si="4"/>
+        <v>24.533333333333331</v>
+      </c>
+      <c r="G81" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4533333333333331E-2</v>
+      </c>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="12"/>
+      <c r="M81" s="3">
+        <f t="shared" ref="M81" si="21">D80/(7/12/3.281)</f>
+        <v>23.229479999999999</v>
+      </c>
+      <c r="N81" s="3">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O81" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="10"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="12">
+        <v>16</v>
+      </c>
+      <c r="D82" s="14">
+        <v>2.82</v>
+      </c>
+      <c r="E82" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F82" s="94">
+        <f t="shared" si="4"/>
+        <v>17.825185185185184</v>
+      </c>
+      <c r="G82" s="94">
+        <f t="shared" si="5"/>
+        <v>1.7825185185185183E-2</v>
+      </c>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="12"/>
+      <c r="M82" s="3">
+        <f t="shared" ref="M82" si="22">D83/(7/12/3.281)</f>
+        <v>16.704977142857143</v>
+      </c>
+      <c r="N82" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O82" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="10"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="12">
+        <v>15</v>
+      </c>
+      <c r="D83" s="14">
+        <v>2.97</v>
+      </c>
+      <c r="E83" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F83" s="94">
+        <f t="shared" si="4"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G83" s="94">
+        <f t="shared" si="5"/>
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="12"/>
+      <c r="M83" s="3">
+        <f t="shared" ref="M83" si="23">D82/(7/12/3.281)</f>
+        <v>15.861291428571427</v>
+      </c>
+      <c r="N83" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="O83" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="10"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="12">
+        <v>16</v>
+      </c>
+      <c r="D84" s="14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E84" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F84" s="94">
+        <f t="shared" si="4"/>
+        <v>25.916049382716047</v>
+      </c>
+      <c r="G84" s="94">
+        <f t="shared" si="5"/>
+        <v>2.5916049382716046E-2</v>
+      </c>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="12"/>
+      <c r="M84" s="3">
+        <f t="shared" ref="M84" si="24">D85/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
+      </c>
+      <c r="N84" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O84" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="10"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="12">
+        <v>23</v>
+      </c>
+      <c r="D85" s="14">
+        <v>2.93</v>
+      </c>
+      <c r="E85" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F85" s="94">
+        <f t="shared" si="4"/>
+        <v>26.623209876543207</v>
+      </c>
+      <c r="G85" s="94">
+        <f t="shared" si="5"/>
+        <v>2.6623209876543208E-2</v>
+      </c>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="12"/>
+      <c r="M85" s="3">
+        <f t="shared" ref="M85" si="25">D84/(7/12/3.281)</f>
+        <v>23.060742857142856</v>
+      </c>
+      <c r="N85" s="3">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O85" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="10"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="12">
+        <v>16</v>
+      </c>
+      <c r="D86" s="14">
+        <v>3.55</v>
+      </c>
+      <c r="E86" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F86" s="94">
+        <f t="shared" si="4"/>
+        <v>22.439506172839504</v>
+      </c>
+      <c r="G86" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2439506172839505E-2</v>
+      </c>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="12"/>
+      <c r="M86" s="3">
+        <f t="shared" ref="M86" si="26">D87/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N86" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O86" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="10"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="12">
+        <v>19</v>
+      </c>
+      <c r="D87" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E87" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F87" s="94">
+        <f t="shared" si="4"/>
+        <v>22.068148148148147</v>
+      </c>
+      <c r="G87" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2068148148148146E-2</v>
+      </c>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="13"/>
+      <c r="K87" s="12"/>
+      <c r="M87" s="3">
+        <f t="shared" ref="M87" si="27">D86/(7/12/3.281)</f>
+        <v>19.967228571428571</v>
+      </c>
+      <c r="N87" s="3">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="O87" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="10"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="12">
+        <v>16</v>
+      </c>
+      <c r="D88" s="14">
+        <v>3.56</v>
+      </c>
+      <c r="E88" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F88" s="94">
+        <f t="shared" si="4"/>
+        <v>22.502716049382716</v>
+      </c>
+      <c r="G88" s="94">
+        <f t="shared" si="5"/>
+        <v>2.2502716049382716E-2</v>
+      </c>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="12"/>
+      <c r="M88" s="3">
+        <f t="shared" ref="M88" si="28">D89/(7/12/3.281)</f>
+        <v>16.536239999999999</v>
+      </c>
+      <c r="N88" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O88" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="10"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="12">
+        <v>20</v>
+      </c>
+      <c r="D89" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="E89" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F89" s="94">
+        <f t="shared" si="4"/>
+        <v>23.229629629629628</v>
+      </c>
+      <c r="G89" s="94">
+        <f t="shared" si="5"/>
+        <v>2.3229629629629628E-2</v>
+      </c>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="13"/>
+      <c r="K89" s="12"/>
+      <c r="M89" s="3">
+        <f t="shared" ref="M89" si="29">D88/(7/12/3.281)</f>
+        <v>20.023474285714286</v>
+      </c>
+      <c r="N89" s="3">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="O89" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="10"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="12">
+        <v>16</v>
+      </c>
+      <c r="D90" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="E90" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F90" s="94">
+        <f t="shared" si="4"/>
+        <v>40.45432098765432</v>
+      </c>
+      <c r="G90" s="94">
+        <f t="shared" si="5"/>
+        <v>4.0454320987654321E-2</v>
+      </c>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="12"/>
+      <c r="M90" s="3">
+        <f t="shared" ref="M90" si="30">D91/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
+      </c>
+      <c r="N90" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O90" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="10"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="12">
+        <v>30</v>
+      </c>
+      <c r="D91" s="14">
+        <v>2.93</v>
+      </c>
+      <c r="E91" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F91" s="94">
+        <f t="shared" si="4"/>
+        <v>34.725925925925928</v>
+      </c>
+      <c r="G91" s="94">
+        <f t="shared" si="5"/>
+        <v>3.4725925925925931E-2</v>
+      </c>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="13"/>
+      <c r="K91" s="12"/>
+      <c r="M91" s="3">
+        <f t="shared" ref="M91" si="31">D90/(7/12/3.281)</f>
+        <v>35.997257142857144</v>
+      </c>
+      <c r="N91" s="3">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="O91" s="3">
+        <f t="shared" si="7"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="10"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="12">
+        <v>16</v>
+      </c>
+      <c r="D92" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="E92" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F92" s="94">
+        <f t="shared" si="4"/>
+        <v>24.019753086419751</v>
+      </c>
+      <c r="G92" s="94">
+        <f t="shared" si="5"/>
+        <v>2.4019753086419751E-2</v>
+      </c>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="13"/>
+      <c r="K92" s="12"/>
+      <c r="M92" s="3">
+        <f t="shared" ref="M92" si="32">D93/(7/12/3.281)</f>
+        <v>16.479994285714287</v>
+      </c>
+      <c r="N92" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="O92" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="10"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="12">
+        <v>20</v>
+      </c>
+      <c r="D93" s="14">
+        <v>2.93</v>
+      </c>
+      <c r="E93" s="14">
+        <f t="shared" si="3"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F93" s="94">
+        <f t="shared" si="4"/>
+        <v>23.150617283950616</v>
+      </c>
+      <c r="G93" s="94">
+        <f t="shared" si="5"/>
+        <v>2.3150617283950615E-2</v>
+      </c>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="12"/>
+      <c r="M93" s="3">
+        <f t="shared" ref="M93" si="33">D92/(7/12/3.281)</f>
+        <v>21.373371428571428</v>
+      </c>
+      <c r="N93" s="3">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="O93" s="3">
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="17"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="95">
+        <f>SUM(G66:G93)</f>
+        <v>0.71455209876543213</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="I94" s="2">
+        <v>124355</v>
+      </c>
+      <c r="J94" s="19">
+        <f>G94*I94</f>
+        <v>88858.126241975318</v>
+      </c>
+      <c r="K94" s="18"/>
+    </row>
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="10"/>
+      <c r="B95" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="13">
+        <f>0.13*G94*110000</f>
+        <v>10218.095012345681</v>
+      </c>
+      <c r="K95" s="12"/>
+    </row>
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10"/>
+      <c r="B96" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="13">
+        <f>0.13*G94*960</f>
+        <v>89.176101925925934</v>
+      </c>
+      <c r="K96" s="12"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="10"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="13"/>
+      <c r="K97" s="12"/>
+    </row>
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="15">
+        <v>5</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98" s="17">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="20">
+        <f t="shared" ref="G98" si="34">PRODUCT(C98:F98)</f>
+        <v>1</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I98" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J98" s="20">
+        <f>G98*I98</f>
+        <v>5000</v>
+      </c>
+      <c r="K98" s="18"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="18"/>
+    </row>
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="15">
+        <v>6</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="17">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="20">
+        <f t="shared" ref="G100" si="35">PRODUCT(C100:F100)</f>
+        <v>1</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="2">
+        <v>500</v>
+      </c>
+      <c r="J100" s="20">
+        <f>G100*I100</f>
+        <v>500</v>
+      </c>
+      <c r="K100" s="18"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="18"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="26"/>
+      <c r="B102" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="28"/>
+      <c r="D102" s="29"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13">
+        <f>SUM(J9:J100)</f>
+        <v>565780.32579845074</v>
+      </c>
+      <c r="K102" s="30"/>
+    </row>
+    <row r="104" spans="1:11" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="31"/>
+      <c r="B104" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="74">
+        <f>J102</f>
+        <v>565780.32579845074</v>
+      </c>
+      <c r="D104" s="75"/>
+      <c r="E104" s="33">
+        <v>100</v>
+      </c>
+      <c r="F104" s="31"/>
+      <c r="G104" s="34"/>
+      <c r="H104" s="31"/>
+      <c r="I104" s="35"/>
+      <c r="J104" s="36"/>
+      <c r="K104" s="37"/>
+    </row>
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="78">
+        <v>500000</v>
+      </c>
+      <c r="D105" s="79"/>
+      <c r="E105" s="33"/>
+    </row>
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="78">
+        <f>C105-C108-C109</f>
+        <v>475000</v>
+      </c>
+      <c r="D106" s="79"/>
+      <c r="E106" s="33">
+        <f>C106/C104*100</f>
+        <v>83.95484578394661</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" s="80">
+        <f>C104-C106</f>
+        <v>90780.325798450736</v>
+      </c>
+      <c r="D107" s="80"/>
+      <c r="E107" s="33">
+        <f>100-E106</f>
+        <v>16.04515421605339</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="74">
+        <f>C105*0.03</f>
+        <v>15000</v>
+      </c>
+      <c r="D108" s="75"/>
+      <c r="E108" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="74">
+        <f>C105*0.02</f>
+        <v>10000</v>
+      </c>
+      <c r="D109" s="75"/>
+      <c r="E109" s="33">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>